--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.1 Excel Driven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F31E3D04097856D80F76C427942304A3B08A4CB6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EF9A07-E90F-4AE1-A568-7198CF69C400}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="498">
   <si>
     <t>AY26-27 Classera Plans | Events Tracker</t>
   </si>
@@ -1531,17 +1531,20 @@
   </si>
   <si>
     <t>Source: plans.classera.com Full Calendar (KSA and Egypt school calendars). No sessions are scheduled inside these periods.</t>
+  </si>
+  <si>
+    <t>https://sh.classera.com/Enrich</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
     <numFmt numFmtId="165" formatCode="mmm\ yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1643,6 +1646,14 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1718,10 +1729,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1819,11 +1831,80 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE0F2FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1941,73 +2022,10 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE0F2FE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{AB7C1172-17F8-40E9-B1DF-04CE91C0F488}"/>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2403,15 +2421,15 @@
       </c>
       <c r="G7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Published")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$U$2:$U$400,"Delivered")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B7)</f>
@@ -2431,7 +2449,7 @@
       </c>
       <c r="N7" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B7,Events!$AG$2:$AG$400,"?*")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -2668,15 +2686,15 @@
       </c>
       <c r="G12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$T$2:$T$400,"Published")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$U$2:$U$400,"Delivered")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
@@ -2696,7 +2714,7 @@
       </c>
       <c r="N12" s="11">
         <f ca="1">COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$AG$2:$AG$400,"?*")</f>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -2730,7 +2748,7 @@
       </c>
       <c r="C16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,C$15)</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,D$15)</f>
@@ -2738,11 +2756,11 @@
       </c>
       <c r="E16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,E$15)</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,F$15)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,G$15)</f>
@@ -2764,7 +2782,7 @@
       </c>
       <c r="C20" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B20)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -3127,10 +3145,10 @@
         <v>Published</v>
       </c>
       <c r="U2" s="30" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>98</v>
+        <v>470</v>
       </c>
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
@@ -3153,7 +3171,7 @@
       </c>
       <c r="AG2" s="28" t="str">
         <f t="shared" ref="AG2:AG33" ca="1" si="7">IF(AND(AE2="Past",U2&lt;&gt;"Delivered",U2&lt;&gt;"Cancelled",U2&lt;&gt;"Postponed"),"Update status",IF(AND(T2="Missing",OR(AE2="In progress",AE2="Next 14 days")),"Add link",IF(AND(AE2="Next 14 days",V2&lt;&gt;"Published"),"Announce","")))</f>
-        <v>Update status</v>
+        <v/>
       </c>
       <c r="AH2" s="28"/>
     </row>
@@ -3211,16 +3229,18 @@
         <v>96</v>
       </c>
       <c r="R3" s="23"/>
-      <c r="S3" s="30"/>
+      <c r="S3" s="41" t="s">
+        <v>497</v>
+      </c>
       <c r="T3" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Missing</v>
+        <v>Published</v>
       </c>
       <c r="U3" s="30" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>98</v>
+        <v>470</v>
       </c>
       <c r="W3" s="30"/>
       <c r="X3" s="31"/>
@@ -3243,7 +3263,7 @@
       </c>
       <c r="AG3" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Update status</v>
+        <v/>
       </c>
       <c r="AH3" s="28"/>
     </row>
@@ -3309,10 +3329,10 @@
         <v>Published</v>
       </c>
       <c r="U4" s="30" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>98</v>
+        <v>470</v>
       </c>
       <c r="W4" s="30"/>
       <c r="X4" s="31"/>
@@ -3335,7 +3355,7 @@
       </c>
       <c r="AG4" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Update status</v>
+        <v/>
       </c>
       <c r="AH4" s="28" t="s">
         <v>110</v>
@@ -8997,7 +9017,7 @@
       <c r="R66" s="23"/>
       <c r="S66" s="30"/>
       <c r="T66" s="28" t="str">
-        <f t="shared" ref="T66:T97" si="19">IF(TRIM(S66)="","Missing","Published")</f>
+        <f t="shared" ref="T66:T81" si="19">IF(TRIM(S66)="","Missing","Published")</f>
         <v>Missing</v>
       </c>
       <c r="U66" s="30" t="s">
@@ -9010,7 +9030,7 @@
       <c r="X66" s="31"/>
       <c r="Y66" s="31"/>
       <c r="Z66" s="32" t="str">
-        <f t="shared" ref="Z66:Z97" si="20">IF(N(X66)&gt;0,N(Y66)/X66,"")</f>
+        <f t="shared" ref="Z66:Z81" si="20">IF(N(X66)&gt;0,N(Y66)/X66,"")</f>
         <v/>
       </c>
       <c r="AA66" s="33"/>
@@ -10352,55 +10372,55 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="T2:T400">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"Missing"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+      <formula>"Published"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="U2:U400">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Delivered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Registration Open"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"Confirmed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"Cancelled"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T400">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
-      <formula>"Missing"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"Published"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="V2:V400">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
       <formula>"Published"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE400">
-    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
       <formula>"Next 14 days"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
       <formula>"Past"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG400">
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
       <formula>"Update status"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
       <formula>"Add link"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="15" operator="equal">
       <formula>"Announce"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10447,11 +10467,12 @@
     <hyperlink ref="S44" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
     <hyperlink ref="S45" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
     <hyperlink ref="S46" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
+    <hyperlink ref="S3" r:id="rId33" xr:uid="{F865062C-29FE-4A16-B08E-9C5893CE10A1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId33"/>
+    <tablePart r:id="rId34"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.1 Excel Driven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6EF9A07-E90F-4AE1-A568-7198CF69C400}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13F6BE32-F481-4F22-88A4-64DAA3266DA5}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Guide" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Guide" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Events" sheetId="3" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" r:id="rId4"/>
-    <sheet name="Off-Periods" sheetId="5" r:id="rId5"/>
+    <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Off-Periods" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1843,71 +1844,6 @@
     <dxf>
       <font>
         <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE0F2FE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1A1A1A"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD1FAE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FF7C2D12"/>
         <name val="Arial"/>
         <charset val="1"/>
@@ -1980,6 +1916,71 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFDE68A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE0F2FE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBEAFE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2103,10 +2104,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10381,46 +10378,46 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U400">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"Delivered"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"Registration Open"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
       <formula>"Confirmed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"Cancelled"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V400">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"Published"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE2:AE400">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
       <formula>"Next 14 days"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"In progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
       <formula>"Past"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2:AG400">
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
       <formula>"Update status"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
       <formula>"Add link"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
       <formula>"Announce"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.1 Excel Driven/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13F6BE32-F481-4F22-88A4-64DAA3266DA5}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EDE76FE-E786-422A-B0EF-DEAEBA1EE045}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="498">
   <si>
     <t>AY26-27 Classera Plans | Events Tracker</t>
   </si>
@@ -340,9 +340,6 @@
     <t>Not started</t>
   </si>
   <si>
-    <t>PD-LW2</t>
-  </si>
-  <si>
     <t>Launch Webinar 2: Enrichment Programs Plan</t>
   </si>
   <si>
@@ -1535,6 +1532,9 @@
   </si>
   <si>
     <t>https://sh.classera.com/Enrich</t>
+  </si>
+  <si>
+    <t>ENR-LW2</t>
   </si>
 </sst>
 </file>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B7,Events!$AE$2:$AE$400,"&lt;&gt;Past",Events!$A$2:$A$400,"&lt;&gt;")</f>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Published")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
@@ -2426,19 +2426,19 @@
       </c>
       <c r="I7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$U$2:$U$400,"Delivered")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B7)</f>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="K7" s="8">
         <f>SUMIFS(Events!$Y$2:$Y$400,Events!$B$2:$B$400,$B7)</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="9" t="str">
+        <v>251</v>
+      </c>
+      <c r="L7" s="9">
         <f t="shared" ref="L7:L12" si="0">IF(J7&gt;0,K7/J7,"-")</f>
-        <v>-</v>
+        <v>0.45471014492753625</v>
       </c>
       <c r="M7" s="9" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0",Events!$B$2:$B$400,$B7),"-")</f>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C9" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B9)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B9,Events!$AE$2:$AE$400,"&lt;&gt;Past",Events!$A$2:$A$400,"&lt;&gt;")</f>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G9" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B9,Events!$T$2:$T$400,"Published")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B9,Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="I9" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B9,Events!$U$2:$U$400,"Delivered")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B9)</f>
@@ -2695,15 +2695,15 @@
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="K12" s="12">
         <f>SUM(Events!$Y$2:$Y$400)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="13" t="str">
+        <v>251</v>
+      </c>
+      <c r="L12" s="13">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>0.45471014492753625</v>
       </c>
       <c r="M12" s="13" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0"),"-")</f>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,C$15)</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,D$15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,E$15)</f>
@@ -3126,7 +3126,9 @@
       <c r="N2" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="O2" s="23"/>
+      <c r="O2" s="23" t="s">
+        <v>124</v>
+      </c>
       <c r="P2" s="23" t="s">
         <v>95</v>
       </c>
@@ -3145,7 +3147,7 @@
         <v>10</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
@@ -3174,19 +3176,19 @@
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>99</v>
+        <v>497</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>89</v>
       </c>
       <c r="D3" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>100</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>101</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>92</v>
@@ -3213,12 +3215,14 @@
         <v>Tue</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="O3" s="23"/>
+      <c r="O3" s="23" t="s">
+        <v>124</v>
+      </c>
       <c r="P3" s="23" t="s">
         <v>95</v>
       </c>
@@ -3227,7 +3231,7 @@
       </c>
       <c r="R3" s="23"/>
       <c r="S3" s="41" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T3" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3237,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W3" s="30"/>
       <c r="X3" s="31"/>
@@ -3266,22 +3270,22 @@
     </row>
     <row r="4" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>106</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>107</v>
       </c>
       <c r="G4" s="26">
         <v>46295</v>
@@ -3308,9 +3312,11 @@
         <v>93</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" s="23"/>
+        <v>107</v>
+      </c>
+      <c r="O4" s="23" t="s">
+        <v>124</v>
+      </c>
       <c r="P4" s="23" t="s">
         <v>95</v>
       </c>
@@ -3319,7 +3325,7 @@
       </c>
       <c r="R4" s="23"/>
       <c r="S4" s="29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T4" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3329,14 +3335,18 @@
         <v>10</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W4" s="30"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="32" t="str">
+      <c r="X4" s="31">
+        <v>552</v>
+      </c>
+      <c r="Y4" s="31">
+        <v>251</v>
+      </c>
+      <c r="Z4" s="32">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.45471014492753625</v>
       </c>
       <c r="AA4" s="33"/>
       <c r="AB4" s="34"/>
@@ -3355,27 +3365,27 @@
         <v/>
       </c>
       <c r="AH4" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>114</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>115</v>
       </c>
       <c r="G5" s="26">
         <v>46309</v>
@@ -3402,10 +3412,10 @@
         <v>93</v>
       </c>
       <c r="N5" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="O5" s="23" t="s">
         <v>116</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>117</v>
       </c>
       <c r="P5" s="23" t="s">
         <v>95</v>
@@ -3420,7 +3430,7 @@
         <v>Missing</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V5" s="30" t="s">
         <v>98</v>
@@ -3449,27 +3459,27 @@
         <v>Add link</v>
       </c>
       <c r="AH5" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="E6" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="F6" s="23" t="s">
         <v>122</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>123</v>
       </c>
       <c r="G6" s="26">
         <v>46323</v>
@@ -3496,10 +3506,10 @@
         <v>93</v>
       </c>
       <c r="N6" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O6" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="P6" s="23" t="s">
         <v>95</v>
@@ -3543,27 +3553,27 @@
         <v/>
       </c>
       <c r="AH6" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D7" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="23" t="s">
         <v>129</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>130</v>
       </c>
       <c r="G7" s="26">
         <v>46337</v>
@@ -3590,10 +3600,10 @@
         <v>93</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P7" s="23" t="s">
         <v>95</v>
@@ -3637,27 +3647,27 @@
         <v/>
       </c>
       <c r="AH7" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D8" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>134</v>
-      </c>
       <c r="F8" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" s="26">
         <v>46365</v>
@@ -3684,10 +3694,10 @@
         <v>93</v>
       </c>
       <c r="N8" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="23" t="s">
         <v>116</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>117</v>
       </c>
       <c r="P8" s="23" t="s">
         <v>95</v>
@@ -3731,27 +3741,27 @@
         <v/>
       </c>
       <c r="AH8" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D9" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="F9" s="23" t="s">
         <v>138</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>139</v>
       </c>
       <c r="G9" s="26">
         <v>46379</v>
@@ -3778,10 +3788,10 @@
         <v>93</v>
       </c>
       <c r="N9" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O9" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="P9" s="23" t="s">
         <v>95</v>
@@ -3825,27 +3835,27 @@
         <v/>
       </c>
       <c r="AH9" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D10" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>143</v>
-      </c>
       <c r="F10" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="26">
         <v>46463</v>
@@ -3872,10 +3882,10 @@
         <v>93</v>
       </c>
       <c r="N10" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="O10" s="23" t="s">
         <v>116</v>
-      </c>
-      <c r="O10" s="23" t="s">
-        <v>117</v>
       </c>
       <c r="P10" s="23" t="s">
         <v>95</v>
@@ -3919,27 +3929,27 @@
         <v/>
       </c>
       <c r="AH10" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="F11" s="23" t="s">
         <v>147</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>148</v>
       </c>
       <c r="G11" s="26">
         <v>46477</v>
@@ -3966,10 +3976,10 @@
         <v>93</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P11" s="23" t="s">
         <v>95</v>
@@ -4013,24 +4023,24 @@
         <v/>
       </c>
       <c r="AH11" s="28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>151</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>152</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="26">
@@ -4058,7 +4068,7 @@
         <v>93</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23" t="s">
@@ -4103,24 +4113,24 @@
         <v/>
       </c>
       <c r="AH12" s="28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>155</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>156</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="26">
@@ -4148,7 +4158,7 @@
         <v>93</v>
       </c>
       <c r="N13" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="23" t="s">
@@ -4193,24 +4203,24 @@
         <v/>
       </c>
       <c r="AH13" s="28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>159</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>160</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="26">
@@ -4238,7 +4248,7 @@
         <v>93</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O14" s="23"/>
       <c r="P14" s="23" t="s">
@@ -4283,27 +4293,27 @@
         <v/>
       </c>
       <c r="AH14" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="E15" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="F15" s="23" t="s">
         <v>165</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>166</v>
       </c>
       <c r="G15" s="26">
         <v>46286</v>
@@ -4328,18 +4338,18 @@
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q15" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R15" s="23"/>
       <c r="S15" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T15" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4349,7 +4359,7 @@
         <v>25</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>98</v>
+        <v>469</v>
       </c>
       <c r="W15" s="30"/>
       <c r="X15" s="31"/>
@@ -4378,22 +4388,22 @@
     </row>
     <row r="16" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D16" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>172</v>
-      </c>
       <c r="F16" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="26">
         <v>46300</v>
@@ -4418,18 +4428,18 @@
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q16" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R16" s="23"/>
       <c r="S16" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T16" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4468,22 +4478,22 @@
     </row>
     <row r="17" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D17" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="E17" s="25" t="s">
-        <v>175</v>
-      </c>
       <c r="F17" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G17" s="26">
         <v>46314</v>
@@ -4508,18 +4518,18 @@
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q17" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R17" s="23"/>
       <c r="S17" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T17" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4558,22 +4568,22 @@
     </row>
     <row r="18" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D18" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E18" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>178</v>
-      </c>
       <c r="F18" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G18" s="26">
         <v>46335</v>
@@ -4598,18 +4608,18 @@
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q18" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R18" s="23"/>
       <c r="S18" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T18" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4648,22 +4658,22 @@
     </row>
     <row r="19" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D19" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="E19" s="25" t="s">
-        <v>181</v>
-      </c>
       <c r="F19" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G19" s="26">
         <v>46349</v>
@@ -4688,18 +4698,18 @@
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q19" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R19" s="23"/>
       <c r="S19" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T19" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4738,22 +4748,22 @@
     </row>
     <row r="20" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D20" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="E20" s="25" t="s">
-        <v>184</v>
-      </c>
       <c r="F20" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" s="26">
         <v>46363</v>
@@ -4778,18 +4788,18 @@
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q20" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R20" s="23"/>
       <c r="S20" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T20" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4828,22 +4838,22 @@
     </row>
     <row r="21" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D21" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="E21" s="25" t="s">
-        <v>187</v>
-      </c>
       <c r="F21" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="26">
         <v>46377</v>
@@ -4868,18 +4878,18 @@
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O21" s="23"/>
       <c r="P21" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q21" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R21" s="23"/>
       <c r="S21" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T21" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4918,22 +4928,22 @@
     </row>
     <row r="22" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D22" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="E22" s="25" t="s">
-        <v>190</v>
-      </c>
       <c r="F22" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G22" s="26">
         <v>46391</v>
@@ -4958,18 +4968,18 @@
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O22" s="23"/>
       <c r="P22" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R22" s="23"/>
       <c r="S22" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T22" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5008,22 +5018,22 @@
     </row>
     <row r="23" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="E23" s="25" t="s">
-        <v>193</v>
-      </c>
       <c r="F23" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G23" s="26">
         <v>46405</v>
@@ -5048,18 +5058,18 @@
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O23" s="23"/>
       <c r="P23" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R23" s="23"/>
       <c r="S23" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T23" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5098,22 +5108,22 @@
     </row>
     <row r="24" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D24" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>196</v>
-      </c>
       <c r="F24" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G24" s="26">
         <v>46426</v>
@@ -5138,18 +5148,18 @@
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O24" s="23"/>
       <c r="P24" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R24" s="23"/>
       <c r="S24" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T24" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5188,22 +5198,22 @@
     </row>
     <row r="25" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D25" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E25" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="25" t="s">
-        <v>199</v>
-      </c>
       <c r="F25" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G25" s="26">
         <v>46440</v>
@@ -5228,18 +5238,18 @@
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O25" s="23"/>
       <c r="P25" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q25" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R25" s="23"/>
       <c r="S25" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T25" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5278,22 +5288,22 @@
     </row>
     <row r="26" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D26" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>202</v>
-      </c>
       <c r="F26" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G26" s="26">
         <v>46454</v>
@@ -5318,18 +5328,18 @@
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q26" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R26" s="23"/>
       <c r="S26" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T26" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5368,22 +5378,22 @@
     </row>
     <row r="27" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D27" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>205</v>
-      </c>
       <c r="F27" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G27" s="26">
         <v>46468</v>
@@ -5408,18 +5418,18 @@
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O27" s="23"/>
       <c r="P27" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q27" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R27" s="23"/>
       <c r="S27" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T27" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5458,22 +5468,22 @@
     </row>
     <row r="28" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D28" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>208</v>
-      </c>
       <c r="F28" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G28" s="26">
         <v>46482</v>
@@ -5498,18 +5508,18 @@
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O28" s="23"/>
       <c r="P28" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q28" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R28" s="23"/>
       <c r="S28" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T28" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5548,22 +5558,22 @@
     </row>
     <row r="29" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D29" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="25" t="s">
-        <v>211</v>
-      </c>
       <c r="F29" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G29" s="26">
         <v>46496</v>
@@ -5588,18 +5598,18 @@
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O29" s="23"/>
       <c r="P29" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q29" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R29" s="23"/>
       <c r="S29" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T29" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5638,22 +5648,22 @@
     </row>
     <row r="30" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D30" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E30" s="25" t="s">
-        <v>214</v>
-      </c>
       <c r="F30" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G30" s="26">
         <v>46510</v>
@@ -5678,18 +5688,18 @@
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O30" s="23"/>
       <c r="P30" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q30" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R30" s="23"/>
       <c r="S30" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T30" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5728,22 +5738,22 @@
     </row>
     <row r="31" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D31" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="25" t="s">
-        <v>217</v>
-      </c>
       <c r="F31" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G31" s="26">
         <v>46531</v>
@@ -5768,18 +5778,18 @@
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q31" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R31" s="23"/>
       <c r="S31" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T31" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5818,22 +5828,22 @@
     </row>
     <row r="32" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D32" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="E32" s="25" t="s">
-        <v>220</v>
-      </c>
       <c r="F32" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G32" s="26">
         <v>46545</v>
@@ -5858,18 +5868,18 @@
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O32" s="23"/>
       <c r="P32" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q32" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R32" s="23"/>
       <c r="S32" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T32" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5908,22 +5918,22 @@
     </row>
     <row r="33" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D33" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="E33" s="25" t="s">
-        <v>223</v>
-      </c>
       <c r="F33" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G33" s="26">
         <v>46559</v>
@@ -5948,18 +5958,18 @@
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O33" s="23"/>
       <c r="P33" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q33" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R33" s="23"/>
       <c r="S33" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T33" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5998,19 +6008,19 @@
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="E34" s="25" t="s">
         <v>226</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>227</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>18</v>
@@ -6038,20 +6048,20 @@
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O34" s="23"/>
       <c r="P34" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q34" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R34" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="S34" s="29" t="s">
         <v>230</v>
-      </c>
-      <c r="S34" s="29" t="s">
-        <v>231</v>
       </c>
       <c r="T34" s="28" t="str">
         <f t="shared" ref="T34:T65" si="11">IF(TRIM(S34)="","Missing","Published")</f>
@@ -6087,24 +6097,24 @@
         <v>Update status</v>
       </c>
       <c r="AH34" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D35" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="25" t="s">
         <v>234</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>235</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>18</v>
@@ -6132,20 +6142,20 @@
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O35" s="23"/>
       <c r="P35" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q35" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T35" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6181,24 +6191,24 @@
         <v>Announce</v>
       </c>
       <c r="AH35" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D36" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="25" t="s">
         <v>240</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>241</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>18</v>
@@ -6226,20 +6236,20 @@
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O36" s="23"/>
       <c r="P36" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q36" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T36" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6275,24 +6285,24 @@
         <v>Announce</v>
       </c>
       <c r="AH36" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="D37" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="E37" s="25" t="s">
         <v>247</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>248</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>18</v>
@@ -6320,20 +6330,20 @@
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O37" s="23"/>
       <c r="P37" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q37" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R37" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="S37" s="29" t="s">
         <v>250</v>
-      </c>
-      <c r="S37" s="29" t="s">
-        <v>251</v>
       </c>
       <c r="T37" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6369,24 +6379,24 @@
         <v>Announce</v>
       </c>
       <c r="AH37" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" s="23" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D38" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="25" t="s">
         <v>254</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>255</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>18</v>
@@ -6414,17 +6424,17 @@
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O38" s="23"/>
       <c r="P38" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q38" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S38" s="30"/>
       <c r="T38" s="28" t="str">
@@ -6461,24 +6471,24 @@
         <v/>
       </c>
       <c r="AH38" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D39" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" s="25" t="s">
         <v>258</v>
-      </c>
-      <c r="E39" s="25" t="s">
-        <v>259</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>18</v>
@@ -6506,20 +6516,20 @@
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O39" s="23"/>
       <c r="P39" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q39" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T39" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6555,24 +6565,24 @@
         <v/>
       </c>
       <c r="AH39" s="28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D40" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E40" s="25" t="s">
         <v>263</v>
-      </c>
-      <c r="E40" s="25" t="s">
-        <v>264</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>18</v>
@@ -6600,20 +6610,20 @@
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O40" s="23"/>
       <c r="P40" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q40" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T40" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6649,24 +6659,24 @@
         <v/>
       </c>
       <c r="AH40" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D41" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="E41" s="25" t="s">
         <v>269</v>
-      </c>
-      <c r="E41" s="25" t="s">
-        <v>270</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>18</v>
@@ -6694,20 +6704,20 @@
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O41" s="23"/>
       <c r="P41" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q41" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R41" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S41" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T41" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6743,24 +6753,24 @@
         <v/>
       </c>
       <c r="AH41" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D42" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E42" s="25" t="s">
         <v>275</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>276</v>
       </c>
       <c r="F42" s="23" t="s">
         <v>18</v>
@@ -6788,17 +6798,17 @@
       </c>
       <c r="M42" s="23"/>
       <c r="N42" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O42" s="23"/>
       <c r="P42" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q42" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S42" s="30"/>
       <c r="T42" s="28" t="str">
@@ -6835,24 +6845,24 @@
         <v/>
       </c>
       <c r="AH42" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D43" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="E43" s="25" t="s">
         <v>279</v>
-      </c>
-      <c r="E43" s="25" t="s">
-        <v>280</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>18</v>
@@ -6880,20 +6890,20 @@
       </c>
       <c r="M43" s="23"/>
       <c r="N43" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O43" s="23"/>
       <c r="P43" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q43" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S43" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T43" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6929,24 +6939,24 @@
         <v/>
       </c>
       <c r="AH43" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" s="23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D44" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="E44" s="25" t="s">
         <v>284</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>285</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>18</v>
@@ -6974,20 +6984,20 @@
       </c>
       <c r="M44" s="23"/>
       <c r="N44" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O44" s="23"/>
       <c r="P44" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q44" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R44" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="S44" s="29" t="s">
         <v>286</v>
-      </c>
-      <c r="S44" s="29" t="s">
-        <v>287</v>
       </c>
       <c r="T44" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7023,24 +7033,24 @@
         <v/>
       </c>
       <c r="AH44" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A45" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B45" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D45" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="E45" s="25" t="s">
         <v>290</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>291</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>18</v>
@@ -7068,20 +7078,20 @@
       </c>
       <c r="M45" s="23"/>
       <c r="N45" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O45" s="23"/>
       <c r="P45" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q45" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R45" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S45" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T45" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7117,24 +7127,24 @@
         <v/>
       </c>
       <c r="AH45" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A46" s="23" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D46" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="E46" s="25" t="s">
         <v>296</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>297</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>18</v>
@@ -7162,20 +7172,20 @@
       </c>
       <c r="M46" s="23"/>
       <c r="N46" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O46" s="23"/>
       <c r="P46" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q46" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R46" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S46" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="T46" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7211,24 +7221,24 @@
         <v/>
       </c>
       <c r="AH46" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D47" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="E47" s="25" t="s">
         <v>301</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>302</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>18</v>
@@ -7256,17 +7266,17 @@
       </c>
       <c r="M47" s="23"/>
       <c r="N47" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O47" s="23"/>
       <c r="P47" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q47" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R47" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S47" s="30"/>
       <c r="T47" s="28" t="str">
@@ -7303,24 +7313,24 @@
         <v/>
       </c>
       <c r="AH47" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D48" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="E48" s="25" t="s">
         <v>305</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>306</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>18</v>
@@ -7348,17 +7358,17 @@
       </c>
       <c r="M48" s="23"/>
       <c r="N48" s="24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O48" s="23"/>
       <c r="P48" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q48" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R48" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S48" s="30"/>
       <c r="T48" s="28" t="str">
@@ -7395,24 +7405,24 @@
         <v/>
       </c>
       <c r="AH48" s="28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A49" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C49" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D49" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="D49" s="24" t="s">
+      <c r="E49" s="25" t="s">
         <v>310</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>311</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>18</v>
@@ -7440,17 +7450,17 @@
       </c>
       <c r="M49" s="23"/>
       <c r="N49" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O49" s="23"/>
       <c r="P49" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q49" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S49" s="30"/>
       <c r="T49" s="28" t="str">
@@ -7487,24 +7497,24 @@
         <v/>
       </c>
       <c r="AH49" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D50" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" s="25" t="s">
         <v>314</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>315</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>18</v>
@@ -7532,17 +7542,17 @@
       </c>
       <c r="M50" s="23"/>
       <c r="N50" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O50" s="23"/>
       <c r="P50" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q50" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S50" s="30"/>
       <c r="T50" s="28" t="str">
@@ -7579,24 +7589,24 @@
         <v/>
       </c>
       <c r="AH50" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D51" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="E51" s="25" t="s">
         <v>318</v>
-      </c>
-      <c r="E51" s="25" t="s">
-        <v>319</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>18</v>
@@ -7624,17 +7634,17 @@
       </c>
       <c r="M51" s="23"/>
       <c r="N51" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O51" s="23"/>
       <c r="P51" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q51" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R51" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S51" s="30"/>
       <c r="T51" s="28" t="str">
@@ -7671,24 +7681,24 @@
         <v/>
       </c>
       <c r="AH51" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D52" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="E52" s="25" t="s">
         <v>322</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>323</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>18</v>
@@ -7716,17 +7726,17 @@
       </c>
       <c r="M52" s="23"/>
       <c r="N52" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O52" s="23"/>
       <c r="P52" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q52" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R52" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S52" s="30"/>
       <c r="T52" s="28" t="str">
@@ -7763,24 +7773,24 @@
         <v/>
       </c>
       <c r="AH52" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B53" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D53" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="E53" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>327</v>
       </c>
       <c r="F53" s="23" t="s">
         <v>18</v>
@@ -7808,17 +7818,17 @@
       </c>
       <c r="M53" s="23"/>
       <c r="N53" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O53" s="23"/>
       <c r="P53" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q53" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R53" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S53" s="30"/>
       <c r="T53" s="28" t="str">
@@ -7855,24 +7865,24 @@
         <v/>
       </c>
       <c r="AH53" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D54" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E54" s="25" t="s">
         <v>330</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>331</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>18</v>
@@ -7900,17 +7910,17 @@
       </c>
       <c r="M54" s="23"/>
       <c r="N54" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O54" s="23"/>
       <c r="P54" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q54" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R54" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S54" s="30"/>
       <c r="T54" s="28" t="str">
@@ -7947,24 +7957,24 @@
         <v/>
       </c>
       <c r="AH54" s="28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B55" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D55" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="E55" s="25" t="s">
         <v>334</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>335</v>
       </c>
       <c r="F55" s="23" t="s">
         <v>18</v>
@@ -7992,17 +8002,17 @@
       </c>
       <c r="M55" s="23"/>
       <c r="N55" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O55" s="23"/>
       <c r="P55" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q55" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R55" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S55" s="30"/>
       <c r="T55" s="28" t="str">
@@ -8039,24 +8049,24 @@
         <v/>
       </c>
       <c r="AH55" s="28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A56" s="23" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B56" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D56" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" s="25" t="s">
         <v>338</v>
-      </c>
-      <c r="E56" s="25" t="s">
-        <v>339</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>18</v>
@@ -8084,17 +8094,17 @@
       </c>
       <c r="M56" s="23"/>
       <c r="N56" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O56" s="23"/>
       <c r="P56" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q56" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R56" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S56" s="30"/>
       <c r="T56" s="28" t="str">
@@ -8131,24 +8141,24 @@
         <v/>
       </c>
       <c r="AH56" s="28" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D57" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="E57" s="25" t="s">
         <v>342</v>
-      </c>
-      <c r="E57" s="25" t="s">
-        <v>343</v>
       </c>
       <c r="F57" s="23" t="s">
         <v>18</v>
@@ -8176,17 +8186,17 @@
       </c>
       <c r="M57" s="23"/>
       <c r="N57" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O57" s="23"/>
       <c r="P57" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q57" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S57" s="30"/>
       <c r="T57" s="28" t="str">
@@ -8223,24 +8233,24 @@
         <v/>
       </c>
       <c r="AH57" s="28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D58" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" s="25" t="s">
         <v>346</v>
-      </c>
-      <c r="E58" s="25" t="s">
-        <v>347</v>
       </c>
       <c r="F58" s="23" t="s">
         <v>18</v>
@@ -8268,17 +8278,17 @@
       </c>
       <c r="M58" s="23"/>
       <c r="N58" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O58" s="23"/>
       <c r="P58" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q58" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R58" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S58" s="30"/>
       <c r="T58" s="28" t="str">
@@ -8315,24 +8325,24 @@
         <v/>
       </c>
       <c r="AH58" s="28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B59" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D59" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="E59" s="25" t="s">
         <v>350</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>351</v>
       </c>
       <c r="F59" s="23" t="s">
         <v>18</v>
@@ -8360,17 +8370,17 @@
       </c>
       <c r="M59" s="23"/>
       <c r="N59" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O59" s="23"/>
       <c r="P59" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q59" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R59" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S59" s="30"/>
       <c r="T59" s="28" t="str">
@@ -8407,24 +8417,24 @@
         <v/>
       </c>
       <c r="AH59" s="28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A60" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D60" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="E60" s="25" t="s">
         <v>354</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>355</v>
       </c>
       <c r="F60" s="23" t="s">
         <v>18</v>
@@ -8452,17 +8462,17 @@
       </c>
       <c r="M60" s="23"/>
       <c r="N60" s="24" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O60" s="23"/>
       <c r="P60" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q60" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R60" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S60" s="30"/>
       <c r="T60" s="28" t="str">
@@ -8499,24 +8509,24 @@
         <v/>
       </c>
       <c r="AH60" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B61" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D61" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="E61" s="25" t="s">
         <v>359</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>360</v>
       </c>
       <c r="F61" s="23" t="s">
         <v>18</v>
@@ -8544,17 +8554,17 @@
       </c>
       <c r="M61" s="23"/>
       <c r="N61" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O61" s="23"/>
       <c r="P61" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q61" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S61" s="30"/>
       <c r="T61" s="28" t="str">
@@ -8591,24 +8601,24 @@
         <v/>
       </c>
       <c r="AH61" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B62" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D62" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="E62" s="25" t="s">
         <v>363</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>364</v>
       </c>
       <c r="F62" s="23" t="s">
         <v>18</v>
@@ -8636,17 +8646,17 @@
       </c>
       <c r="M62" s="23"/>
       <c r="N62" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O62" s="23"/>
       <c r="P62" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q62" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S62" s="30"/>
       <c r="T62" s="28" t="str">
@@ -8683,24 +8693,24 @@
         <v/>
       </c>
       <c r="AH62" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B63" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D63" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="E63" s="25" t="s">
         <v>367</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>368</v>
       </c>
       <c r="F63" s="23" t="s">
         <v>18</v>
@@ -8728,17 +8738,17 @@
       </c>
       <c r="M63" s="23"/>
       <c r="N63" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O63" s="23"/>
       <c r="P63" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q63" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S63" s="30"/>
       <c r="T63" s="28" t="str">
@@ -8775,24 +8785,24 @@
         <v/>
       </c>
       <c r="AH63" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A64" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D64" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="E64" s="25" t="s">
         <v>371</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>372</v>
       </c>
       <c r="F64" s="23" t="s">
         <v>18</v>
@@ -8820,17 +8830,17 @@
       </c>
       <c r="M64" s="23"/>
       <c r="N64" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O64" s="23"/>
       <c r="P64" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q64" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R64" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S64" s="30"/>
       <c r="T64" s="28" t="str">
@@ -8867,24 +8877,24 @@
         <v/>
       </c>
       <c r="AH64" s="28" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D65" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="E65" s="25" t="s">
         <v>376</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>377</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>18</v>
@@ -8912,17 +8922,17 @@
       </c>
       <c r="M65" s="23"/>
       <c r="N65" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O65" s="23"/>
       <c r="P65" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q65" s="23" t="s">
         <v>96</v>
       </c>
       <c r="R65" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S65" s="30"/>
       <c r="T65" s="28" t="str">
@@ -8959,27 +8969,27 @@
         <v/>
       </c>
       <c r="AH65" s="28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>380</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="E66" s="25" t="s">
         <v>381</v>
       </c>
-      <c r="E66" s="25" t="s">
+      <c r="F66" s="23" t="s">
         <v>382</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>383</v>
       </c>
       <c r="G66" s="26">
         <v>46321</v>
@@ -9004,7 +9014,7 @@
       </c>
       <c r="M66" s="23"/>
       <c r="N66" s="24" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O66" s="23"/>
       <c r="P66" s="23"/>
@@ -9047,27 +9057,27 @@
         <v/>
       </c>
       <c r="AH66" s="28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A67" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B67" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C67" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>387</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="E67" s="25" t="s">
         <v>388</v>
       </c>
-      <c r="E67" s="25" t="s">
-        <v>389</v>
-      </c>
       <c r="F67" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G67" s="26">
         <v>46419</v>
@@ -9092,7 +9102,7 @@
       </c>
       <c r="M67" s="23"/>
       <c r="N67" s="24" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O67" s="23"/>
       <c r="P67" s="23"/>
@@ -9135,27 +9145,27 @@
         <v/>
       </c>
       <c r="AH67" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="23" t="s">
+        <v>391</v>
+      </c>
+      <c r="D68" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="E68" s="25" t="s">
         <v>393</v>
       </c>
-      <c r="E68" s="25" t="s">
+      <c r="F68" s="23" t="s">
         <v>394</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>395</v>
       </c>
       <c r="G68" s="26">
         <v>46419</v>
@@ -9164,7 +9174,7 @@
         <v>46446</v>
       </c>
       <c r="I68" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J68" s="27">
         <f t="shared" si="16"/>
@@ -9180,7 +9190,7 @@
       </c>
       <c r="M68" s="23"/>
       <c r="N68" s="24" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O68" s="23"/>
       <c r="P68" s="23"/>
@@ -9223,27 +9233,27 @@
         <v/>
       </c>
       <c r="AH68" s="28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D69" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="E69" s="25" t="s">
         <v>400</v>
       </c>
-      <c r="E69" s="25" t="s">
-        <v>401</v>
-      </c>
       <c r="F69" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G69" s="26">
         <v>46497</v>
@@ -9268,7 +9278,7 @@
       </c>
       <c r="M69" s="23"/>
       <c r="N69" s="24" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O69" s="23"/>
       <c r="P69" s="23"/>
@@ -9311,27 +9321,27 @@
         <v/>
       </c>
       <c r="AH69" s="28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A70" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C70" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="D70" s="24" t="s">
         <v>404</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="E70" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="E70" s="25" t="s">
+      <c r="F70" s="23" t="s">
         <v>406</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>407</v>
       </c>
       <c r="G70" s="26">
         <v>46357</v>
@@ -9340,7 +9350,7 @@
         <v>46387</v>
       </c>
       <c r="I70" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J70" s="27">
         <f t="shared" si="16"/>
@@ -9358,10 +9368,10 @@
       <c r="N70" s="24"/>
       <c r="O70" s="23"/>
       <c r="P70" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q70" s="23" t="s">
         <v>408</v>
-      </c>
-      <c r="Q70" s="23" t="s">
-        <v>409</v>
       </c>
       <c r="R70" s="23"/>
       <c r="S70" s="30"/>
@@ -9399,27 +9409,27 @@
         <v/>
       </c>
       <c r="AH70" s="28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="71" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D71" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="E71" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="E71" s="25" t="s">
-        <v>413</v>
-      </c>
       <c r="F71" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G71" s="26">
         <v>46357</v>
@@ -9428,7 +9438,7 @@
         <v>46387</v>
       </c>
       <c r="I71" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J71" s="27">
         <f t="shared" si="16"/>
@@ -9446,10 +9456,10 @@
       <c r="N71" s="24"/>
       <c r="O71" s="23"/>
       <c r="P71" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q71" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R71" s="23"/>
       <c r="S71" s="30"/>
@@ -9487,27 +9497,27 @@
         <v/>
       </c>
       <c r="AH71" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A72" s="23" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C72" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="D72" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="D72" s="24" t="s">
+      <c r="E72" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="E72" s="25" t="s">
+      <c r="F72" s="23" t="s">
         <v>418</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>419</v>
       </c>
       <c r="G72" s="26">
         <v>46388</v>
@@ -9516,7 +9526,7 @@
         <v>46418</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J72" s="27">
         <f t="shared" si="16"/>
@@ -9534,10 +9544,10 @@
       <c r="N72" s="24"/>
       <c r="O72" s="23"/>
       <c r="P72" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R72" s="23"/>
       <c r="S72" s="30"/>
@@ -9575,27 +9585,27 @@
         <v/>
       </c>
       <c r="AH72" s="28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A73" s="23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="D73" s="24" t="s">
         <v>423</v>
       </c>
-      <c r="D73" s="24" t="s">
+      <c r="E73" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="E73" s="25" t="s">
-        <v>425</v>
-      </c>
       <c r="F73" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G73" s="26">
         <v>46419</v>
@@ -9604,7 +9614,7 @@
         <v>46446</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J73" s="27">
         <f t="shared" si="16"/>
@@ -9622,10 +9632,10 @@
       <c r="N73" s="24"/>
       <c r="O73" s="23"/>
       <c r="P73" s="23" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q73" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R73" s="23"/>
       <c r="S73" s="30"/>
@@ -9663,27 +9673,27 @@
         <v/>
       </c>
       <c r="AH73" s="28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A74" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C74" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="D74" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="E74" s="25" t="s">
         <v>430</v>
       </c>
-      <c r="E74" s="25" t="s">
-        <v>431</v>
-      </c>
       <c r="F74" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G74" s="26">
         <v>46447</v>
@@ -9692,7 +9702,7 @@
         <v>46477</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J74" s="27">
         <f t="shared" si="16"/>
@@ -9710,10 +9720,10 @@
       <c r="N74" s="24"/>
       <c r="O74" s="23"/>
       <c r="P74" s="23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q74" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R74" s="23"/>
       <c r="S74" s="30"/>
@@ -9751,27 +9761,27 @@
         <v/>
       </c>
       <c r="AH74" s="28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A75" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D75" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="E75" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="E75" s="25" t="s">
-        <v>436</v>
-      </c>
       <c r="F75" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G75" s="26">
         <v>46447</v>
@@ -9780,7 +9790,7 @@
         <v>46477</v>
       </c>
       <c r="I75" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J75" s="27">
         <f t="shared" si="16"/>
@@ -9798,10 +9808,10 @@
       <c r="N75" s="24"/>
       <c r="O75" s="23"/>
       <c r="P75" s="23" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q75" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R75" s="23"/>
       <c r="S75" s="30"/>
@@ -9839,27 +9849,27 @@
         <v/>
       </c>
       <c r="AH75" s="28" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A76" s="23" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B76" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D76" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="E76" s="25" t="s">
         <v>440</v>
       </c>
-      <c r="E76" s="25" t="s">
-        <v>441</v>
-      </c>
       <c r="F76" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G76" s="26">
         <v>46478</v>
@@ -9868,7 +9878,7 @@
         <v>46507</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J76" s="27">
         <f t="shared" si="16"/>
@@ -9886,10 +9896,10 @@
       <c r="N76" s="24"/>
       <c r="O76" s="23"/>
       <c r="P76" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R76" s="23"/>
       <c r="S76" s="30"/>
@@ -9927,27 +9937,27 @@
         <v/>
       </c>
       <c r="AH76" s="28" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A77" s="23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B77" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D77" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="E77" s="25" t="s">
         <v>444</v>
       </c>
-      <c r="E77" s="25" t="s">
-        <v>445</v>
-      </c>
       <c r="F77" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G77" s="26">
         <v>46478</v>
@@ -9956,7 +9966,7 @@
         <v>46507</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J77" s="27">
         <f t="shared" si="16"/>
@@ -9974,10 +9984,10 @@
       <c r="N77" s="24"/>
       <c r="O77" s="23"/>
       <c r="P77" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q77" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R77" s="23"/>
       <c r="S77" s="30"/>
@@ -10015,27 +10025,27 @@
         <v/>
       </c>
       <c r="AH77" s="28" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D78" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="E78" s="25" t="s">
         <v>448</v>
       </c>
-      <c r="E78" s="25" t="s">
-        <v>449</v>
-      </c>
       <c r="F78" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G78" s="26">
         <v>46478</v>
@@ -10044,7 +10054,7 @@
         <v>46507</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J78" s="27">
         <f t="shared" si="16"/>
@@ -10062,10 +10072,10 @@
       <c r="N78" s="24"/>
       <c r="O78" s="23"/>
       <c r="P78" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R78" s="23"/>
       <c r="S78" s="30"/>
@@ -10103,27 +10113,27 @@
         <v/>
       </c>
       <c r="AH78" s="28" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A79" s="23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D79" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="E79" s="25" t="s">
         <v>452</v>
       </c>
-      <c r="E79" s="25" t="s">
-        <v>453</v>
-      </c>
       <c r="F79" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G79" s="26">
         <v>46489</v>
@@ -10151,7 +10161,7 @@
       <c r="O79" s="23"/>
       <c r="P79" s="23"/>
       <c r="Q79" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R79" s="23"/>
       <c r="S79" s="30"/>
@@ -10189,27 +10199,27 @@
         <v/>
       </c>
       <c r="AH79" s="28" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A80" s="23" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D80" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E80" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="E80" s="25" t="s">
-        <v>457</v>
-      </c>
       <c r="F80" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G80" s="26">
         <v>46508</v>
@@ -10218,7 +10228,7 @@
         <v>46538</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J80" s="27">
         <f t="shared" si="16"/>
@@ -10236,10 +10246,10 @@
       <c r="N80" s="24"/>
       <c r="O80" s="23"/>
       <c r="P80" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R80" s="23"/>
       <c r="S80" s="30"/>
@@ -10277,27 +10287,27 @@
         <v/>
       </c>
       <c r="AH80" s="28" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B81" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D81" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="E81" s="25" t="s">
         <v>460</v>
       </c>
-      <c r="E81" s="25" t="s">
-        <v>461</v>
-      </c>
       <c r="F81" s="23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G81" s="26">
         <v>46508</v>
@@ -10306,7 +10316,7 @@
         <v>46538</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J81" s="27">
         <f t="shared" si="16"/>
@@ -10324,10 +10334,10 @@
       <c r="N81" s="24"/>
       <c r="O81" s="23"/>
       <c r="P81" s="23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q81" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="R81" s="23"/>
       <c r="S81" s="30"/>
@@ -10365,7 +10375,7 @@
         <v/>
       </c>
       <c r="AH81" s="28" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -10579,7 +10589,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10590,16 +10600,16 @@
         <v>24</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10610,16 +10620,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="D4" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="E4" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>467</v>
-      </c>
       <c r="F4" s="37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10630,10 +10640,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="F5" s="37" t="s">
         <v>468</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10644,7 +10654,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10671,22 +10681,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="36" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="C1" s="36" t="s">
         <v>472</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="D1" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="E1" s="36" t="s">
         <v>474</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="F1" s="36" t="s">
         <v>475</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10697,13 +10707,13 @@
         <v>46291</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="39" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="39" t="s">
-        <v>478</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F11" si="0">B2-A2+1</f>
@@ -10718,13 +10728,13 @@
         <v>46354</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D3" s="39" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="39" t="s">
-        <v>480</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" si="0"/>
@@ -10739,13 +10749,13 @@
         <v>46395</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="39" t="s">
         <v>481</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>482</v>
-      </c>
       <c r="E4" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
@@ -10760,13 +10770,13 @@
         <v>46403</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>483</v>
       </c>
-      <c r="D5" s="39" t="s">
-        <v>484</v>
-      </c>
       <c r="E5" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="0"/>
@@ -10781,13 +10791,13 @@
         <v>46408</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>485</v>
       </c>
-      <c r="D6" s="39" t="s">
-        <v>486</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="0"/>
@@ -10802,13 +10812,13 @@
         <v>46422</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="0"/>
@@ -10823,13 +10833,13 @@
         <v>46440</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="D8" s="39" t="s">
-        <v>489</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="0"/>
@@ -10844,13 +10854,13 @@
         <v>46459</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D9" s="39" t="s">
         <v>490</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>491</v>
-      </c>
       <c r="E9" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
@@ -10865,13 +10875,13 @@
         <v>46529</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="D10" s="39" t="s">
         <v>492</v>
       </c>
-      <c r="D10" s="39" t="s">
-        <v>493</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
@@ -10886,13 +10896,13 @@
         <v>46534</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="D11" s="39" t="s">
         <v>494</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>495</v>
-      </c>
       <c r="E11" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="0"/>
@@ -10901,7 +10911,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EDE76FE-E786-422A-B0EF-DEAEBA1EE045}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C329529-EE18-4249-8EA5-10D8E4CF7C03}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="N9" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B9,Events!$AG$2:$AG$400,"?*")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="N12" s="11">
         <f ca="1">COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$AG$2:$AG$400,"?*")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C22" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B22)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>34</v>
@@ -6071,7 +6071,7 @@
         <v>25</v>
       </c>
       <c r="V34" s="30" t="s">
-        <v>98</v>
+        <v>469</v>
       </c>
       <c r="W34" s="30"/>
       <c r="X34" s="31"/>
@@ -6165,7 +6165,7 @@
         <v>25</v>
       </c>
       <c r="V35" s="30" t="s">
-        <v>98</v>
+        <v>469</v>
       </c>
       <c r="W35" s="30"/>
       <c r="X35" s="31"/>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AG35" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>Announce</v>
+        <v/>
       </c>
       <c r="AH35" s="28" t="s">
         <v>237</v>
@@ -6259,7 +6259,7 @@
         <v>25</v>
       </c>
       <c r="V36" s="30" t="s">
-        <v>98</v>
+        <v>469</v>
       </c>
       <c r="W36" s="30"/>
       <c r="X36" s="31"/>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AG36" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v>Announce</v>
+        <v/>
       </c>
       <c r="AH36" s="28" t="s">
         <v>243</v>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C329529-EE18-4249-8EA5-10D8E4CF7C03}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1383A1FB-AB4C-49A2-B86B-FDF06D9E7687}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="I8" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B8,Events!$U$2:$U$400,"Delivered")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B8)</f>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="N8" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B8,Events!$AG$2:$AG$400,"?*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$U$2:$U$400,"Delivered")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="N12" s="11">
         <f ca="1">COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$AG$2:$AG$400,"?*")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -2753,11 +2753,11 @@
       </c>
       <c r="E16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,E$15)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,F$15)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,G$15)</f>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C20" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B20)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -4356,7 +4356,7 @@
         <v>Published</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="V15" s="30" t="s">
         <v>469</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AG15" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Update status</v>
+        <v/>
       </c>
       <c r="AH15" s="28"/>
     </row>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1383A1FB-AB4C-49A2-B86B-FDF06D9E7687}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E833A5F-2A8A-44B7-8DB8-62EB9CEB2AC9}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -22,6 +22,9 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="499">
   <si>
     <t>AY26-27 Classera Plans | Events Tracker</t>
   </si>
@@ -307,6 +310,9 @@
     <t>Action Flag</t>
   </si>
   <si>
+    <t xml:space="preserve">Title </t>
+  </si>
+  <si>
     <t>PD-LW1</t>
   </si>
   <si>
@@ -328,6 +334,9 @@
     <t>Teachers + School Leaders</t>
   </si>
   <si>
+    <t>Arabic</t>
+  </si>
+  <si>
     <t>Online - Classera Innovation Platform</t>
   </si>
   <si>
@@ -337,63 +346,72 @@
     <t>https://sh.classera.com/EPD</t>
   </si>
   <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>ENR-LW2</t>
+  </si>
+  <si>
+    <t>Launch Webinar 2: Enrichment Programs Plan</t>
+  </si>
+  <si>
+    <t>الويبينار التعريفي الثاني: خطة البرامج الإثرائية</t>
+  </si>
+  <si>
+    <t>10:00 AM</t>
+  </si>
+  <si>
+    <t>https://sh.classera.com/Enrich</t>
+  </si>
+  <si>
+    <t>PD-S01</t>
+  </si>
+  <si>
+    <t>Classera LMS</t>
+  </si>
+  <si>
+    <t>Academic Year Kickoff &amp; Classera LMS Updates — New Features &amp; Release Highlights</t>
+  </si>
+  <si>
+    <t>انطلاقة العام الأكاديمي وتحديثات نظام كلاسيرا — المزايا الجديدة وأبرز الإصدارات</t>
+  </si>
+  <si>
+    <t>Classera</t>
+  </si>
+  <si>
+    <t>All LMS Users</t>
+  </si>
+  <si>
+    <t>https://sh.classera.com/v17unlocked</t>
+  </si>
+  <si>
+    <t>pd-s01</t>
+  </si>
+  <si>
+    <t>PD-S02</t>
+  </si>
+  <si>
+    <t>Intel SFI</t>
+  </si>
+  <si>
+    <t>Intel Skills for Innovation (SFI) Webinar 1 — AI Professional Development</t>
+  </si>
+  <si>
+    <t>Intel Skills for Innovation — التطوير المهني في الذكاء الاصطناعي (1)</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>Teachers</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
     <t>Not started</t>
   </si>
   <si>
-    <t>Launch Webinar 2: Enrichment Programs Plan</t>
-  </si>
-  <si>
-    <t>الويبينار التعريفي الثاني: خطة البرامج الإثرائية</t>
-  </si>
-  <si>
-    <t>10:00 AM</t>
-  </si>
-  <si>
-    <t>PD-S01</t>
-  </si>
-  <si>
-    <t>Classera LMS</t>
-  </si>
-  <si>
-    <t>Academic Year Kickoff &amp; Classera LMS Updates — New Features &amp; Release Highlights</t>
-  </si>
-  <si>
-    <t>انطلاقة العام الأكاديمي وتحديثات نظام كلاسيرا — المزايا الجديدة وأبرز الإصدارات</t>
-  </si>
-  <si>
-    <t>Classera</t>
-  </si>
-  <si>
-    <t>All LMS Users</t>
-  </si>
-  <si>
-    <t>https://sh.classera.com/v17unlocked</t>
-  </si>
-  <si>
-    <t>pd-s01</t>
-  </si>
-  <si>
-    <t>PD-S02</t>
-  </si>
-  <si>
-    <t>Intel SFI</t>
-  </si>
-  <si>
-    <t>Intel Skills for Innovation (SFI) Webinar 1 — AI Professional Development</t>
-  </si>
-  <si>
-    <t>Intel Skills for Innovation — التطوير المهني في الذكاء الاصطناعي (1)</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>Teachers</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
     <t>pd-s02</t>
   </si>
   <si>
@@ -415,9 +433,6 @@
     <t>Teachers &amp; Supervisors</t>
   </si>
   <si>
-    <t>Arabic</t>
-  </si>
-  <si>
     <t>pd-s03</t>
   </si>
   <si>
@@ -1450,9 +1465,6 @@
     <t>Paid</t>
   </si>
   <si>
-    <t>Published</t>
-  </si>
-  <si>
     <t>From</t>
   </si>
   <si>
@@ -1529,12 +1541,6 @@
   </si>
   <si>
     <t>Source: plans.classera.com Full Calendar (KSA and Egypt school calendars). No sessions are scheduled inside these periods.</t>
-  </si>
-  <si>
-    <t>https://sh.classera.com/Enrich</t>
-  </si>
-  <si>
-    <t>ENR-LW2</t>
   </si>
 </sst>
 </file>
@@ -1558,94 +1564,94 @@
       <sz val="18"/>
       <color rgb="FF0B2545"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF0B2545"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF0B2545"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFB91C1C"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF0B2545"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF0B2545"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0563C1"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -2107,9 +2113,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblEvents" displayName="tblEvents" ref="A1:AH81" totalsRowShown="0">
-  <autoFilter ref="A1:AH81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblEvents" displayName="tblEvents" ref="A1:AI81" totalsRowShown="0">
+  <autoFilter ref="A1:AI81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Event ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Program"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Track"/>
@@ -2144,6 +2150,7 @@
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Days to Go"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Action Flag"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Site Key"/>
+    <tableColumn id="35" xr3:uid="{902163A8-38E7-45A3-A858-3838CC641899}" name="Title "/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2352,7 +2359,7 @@
       </c>
       <c r="C4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2536,15 +2543,15 @@
       </c>
       <c r="J9" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B9)</f>
-        <v>0</v>
+        <v>1331</v>
       </c>
       <c r="K9" s="8">
         <f>SUMIFS(Events!$Y$2:$Y$400,Events!$B$2:$B$400,$B9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="9" t="str">
+        <v>746</v>
+      </c>
+      <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>0.56048084147257704</v>
       </c>
       <c r="M9" s="9" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0",Events!$B$2:$B$400,$B9),"-")</f>
@@ -2695,15 +2702,15 @@
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
-        <v>552</v>
+        <v>1883</v>
       </c>
       <c r="K12" s="12">
         <f>SUM(Events!$Y$2:$Y$400)</f>
-        <v>251</v>
+        <v>997</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="0"/>
-        <v>0.45471014492753625</v>
+        <v>0.52947424322889003</v>
       </c>
       <c r="M12" s="13" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0"),"-")</f>
@@ -2779,7 +2786,7 @@
       </c>
       <c r="C20" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B20)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -2803,7 +2810,7 @@
       </c>
       <c r="C22" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B22)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>34</v>
@@ -2942,12 +2949,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH81"/>
+  <dimension ref="A1:AI81"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
@@ -2976,7 +2984,7 @@
     <col min="34" max="34" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>62</v>
       </c>
@@ -3079,25 +3087,28 @@
       <c r="AH1" s="21" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" s="26">
         <v>46293</v>
@@ -3121,23 +3132,23 @@
         <v>Mon</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O2" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P2" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R2" s="23"/>
       <c r="S2" s="29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T2" s="28" t="str">
         <f t="shared" ref="T2:T33" si="3">IF(TRIM(S2)="","Missing","Published")</f>
@@ -3147,7 +3158,7 @@
         <v>10</v>
       </c>
       <c r="V2" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
@@ -3174,24 +3185,24 @@
       </c>
       <c r="AH2" s="28"/>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>497</v>
+        <v>101</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3" s="26">
         <v>46294</v>
@@ -3215,23 +3226,23 @@
         <v>Tue</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N3" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R3" s="23"/>
       <c r="S3" s="41" t="s">
-        <v>496</v>
+        <v>105</v>
       </c>
       <c r="T3" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3241,7 +3252,7 @@
         <v>10</v>
       </c>
       <c r="V3" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W3" s="30"/>
       <c r="X3" s="31"/>
@@ -3268,24 +3279,24 @@
       </c>
       <c r="AH3" s="28"/>
     </row>
-    <row r="4" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G4" s="26">
         <v>46295</v>
@@ -3309,23 +3320,23 @@
         <v>Wed</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P4" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q4" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R4" s="23"/>
       <c r="S4" s="29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="T4" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3335,7 +3346,7 @@
         <v>10</v>
       </c>
       <c r="V4" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W4" s="30"/>
       <c r="X4" s="31">
@@ -3365,27 +3376,27 @@
         <v/>
       </c>
       <c r="AH4" s="28" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G5" s="26">
         <v>46309</v>
@@ -3409,19 +3420,19 @@
         <v>Wed</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N5" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P5" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R5" s="23"/>
       <c r="S5" s="30"/>
@@ -3433,7 +3444,7 @@
         <v>24</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W5" s="30"/>
       <c r="X5" s="31"/>
@@ -3452,34 +3463,34 @@
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AG5" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>Add link</v>
       </c>
       <c r="AH5" s="28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G6" s="26">
         <v>46323</v>
@@ -3503,19 +3514,19 @@
         <v>Wed</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P6" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R6" s="23"/>
       <c r="S6" s="30"/>
@@ -3527,7 +3538,7 @@
         <v>23</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W6" s="30"/>
       <c r="X6" s="31"/>
@@ -3546,34 +3557,34 @@
       </c>
       <c r="AF6" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG6" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH6" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G7" s="26">
         <v>46337</v>
@@ -3597,19 +3608,19 @@
         <v>Wed</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P7" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R7" s="23"/>
       <c r="S7" s="30"/>
@@ -3621,7 +3632,7 @@
         <v>23</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W7" s="30"/>
       <c r="X7" s="31"/>
@@ -3640,34 +3651,34 @@
       </c>
       <c r="AF7" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AG7" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH7" s="28" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G8" s="26">
         <v>46365</v>
@@ -3691,19 +3702,19 @@
         <v>Wed</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R8" s="23"/>
       <c r="S8" s="30"/>
@@ -3715,7 +3726,7 @@
         <v>23</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W8" s="30"/>
       <c r="X8" s="31"/>
@@ -3734,34 +3745,34 @@
       </c>
       <c r="AF8" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AG8" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH8" s="28" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G9" s="26">
         <v>46379</v>
@@ -3785,19 +3796,19 @@
         <v>Wed</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R9" s="23"/>
       <c r="S9" s="30"/>
@@ -3809,7 +3820,7 @@
         <v>23</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W9" s="30"/>
       <c r="X9" s="31"/>
@@ -3828,34 +3839,34 @@
       </c>
       <c r="AF9" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AG9" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH9" s="28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G10" s="26">
         <v>46463</v>
@@ -3879,19 +3890,19 @@
         <v>Wed</v>
       </c>
       <c r="M10" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P10" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R10" s="23"/>
       <c r="S10" s="30"/>
@@ -3903,7 +3914,7 @@
         <v>23</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W10" s="30"/>
       <c r="X10" s="31"/>
@@ -3922,34 +3933,34 @@
       </c>
       <c r="AF10" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AG10" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH10" s="28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G11" s="26">
         <v>46477</v>
@@ -3973,19 +3984,19 @@
         <v>Wed</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N11" s="24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="P11" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R11" s="23"/>
       <c r="S11" s="30"/>
@@ -3997,7 +4008,7 @@
         <v>23</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W11" s="30"/>
       <c r="X11" s="31"/>
@@ -4016,31 +4027,31 @@
       </c>
       <c r="AF11" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG11" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH11" s="28" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="26">
@@ -4065,17 +4076,17 @@
         <v>Wed</v>
       </c>
       <c r="M12" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R12" s="23"/>
       <c r="S12" s="30"/>
@@ -4087,7 +4098,7 @@
         <v>23</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W12" s="30"/>
       <c r="X12" s="31"/>
@@ -4106,31 +4117,31 @@
       </c>
       <c r="AF12" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AG12" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH12" s="28" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="26">
@@ -4155,17 +4166,17 @@
         <v>Wed</v>
       </c>
       <c r="M13" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N13" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R13" s="23"/>
       <c r="S13" s="30"/>
@@ -4177,7 +4188,7 @@
         <v>23</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W13" s="30"/>
       <c r="X13" s="31"/>
@@ -4196,31 +4207,31 @@
       </c>
       <c r="AF13" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG13" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH13" s="28" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="26">
@@ -4245,17 +4256,17 @@
         <v>Wed</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O14" s="23"/>
       <c r="P14" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R14" s="23"/>
       <c r="S14" s="30"/>
@@ -4267,7 +4278,7 @@
         <v>23</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W14" s="30"/>
       <c r="X14" s="31"/>
@@ -4286,34 +4297,34 @@
       </c>
       <c r="AF14" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG14" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH14" s="28" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G15" s="26">
         <v>46286</v>
@@ -4338,18 +4349,18 @@
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R15" s="23"/>
       <c r="S15" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T15" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4359,7 +4370,7 @@
         <v>10</v>
       </c>
       <c r="V15" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W15" s="30"/>
       <c r="X15" s="31"/>
@@ -4386,24 +4397,24 @@
       </c>
       <c r="AH15" s="28"/>
     </row>
-    <row r="16" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G16" s="26">
         <v>46300</v>
@@ -4428,18 +4439,18 @@
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q16" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R16" s="23"/>
       <c r="S16" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T16" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4449,7 +4460,7 @@
         <v>25</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W16" s="30"/>
       <c r="X16" s="31"/>
@@ -4468,7 +4479,7 @@
       </c>
       <c r="AF16" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4478,22 +4489,22 @@
     </row>
     <row r="17" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G17" s="26">
         <v>46314</v>
@@ -4518,18 +4529,18 @@
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q17" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R17" s="23"/>
       <c r="S17" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T17" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4539,7 +4550,7 @@
         <v>25</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W17" s="30"/>
       <c r="X17" s="31"/>
@@ -4558,7 +4569,7 @@
       </c>
       <c r="AF17" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AG17" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4568,22 +4579,22 @@
     </row>
     <row r="18" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G18" s="26">
         <v>46335</v>
@@ -4608,18 +4619,18 @@
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q18" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R18" s="23"/>
       <c r="S18" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T18" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4629,7 +4640,7 @@
         <v>25</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W18" s="30"/>
       <c r="X18" s="31"/>
@@ -4648,7 +4659,7 @@
       </c>
       <c r="AF18" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AG18" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4658,22 +4669,22 @@
     </row>
     <row r="19" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G19" s="26">
         <v>46349</v>
@@ -4698,18 +4709,18 @@
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q19" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R19" s="23"/>
       <c r="S19" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T19" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4719,7 +4730,7 @@
         <v>25</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W19" s="30"/>
       <c r="X19" s="31"/>
@@ -4738,7 +4749,7 @@
       </c>
       <c r="AF19" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG19" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4748,22 +4759,22 @@
     </row>
     <row r="20" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G20" s="26">
         <v>46363</v>
@@ -4788,18 +4799,18 @@
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q20" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R20" s="23"/>
       <c r="S20" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T20" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4809,7 +4820,7 @@
         <v>25</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W20" s="30"/>
       <c r="X20" s="31"/>
@@ -4828,7 +4839,7 @@
       </c>
       <c r="AF20" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AG20" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4838,22 +4849,22 @@
     </row>
     <row r="21" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G21" s="26">
         <v>46377</v>
@@ -4878,18 +4889,18 @@
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O21" s="23"/>
       <c r="P21" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q21" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R21" s="23"/>
       <c r="S21" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T21" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4899,7 +4910,7 @@
         <v>25</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W21" s="30"/>
       <c r="X21" s="31"/>
@@ -4918,7 +4929,7 @@
       </c>
       <c r="AF21" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG21" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4928,22 +4939,22 @@
     </row>
     <row r="22" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G22" s="26">
         <v>46391</v>
@@ -4968,18 +4979,18 @@
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O22" s="23"/>
       <c r="P22" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q22" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R22" s="23"/>
       <c r="S22" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T22" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4989,7 +5000,7 @@
         <v>25</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W22" s="30"/>
       <c r="X22" s="31"/>
@@ -5008,7 +5019,7 @@
       </c>
       <c r="AF22" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AG22" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5018,22 +5029,22 @@
     </row>
     <row r="23" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G23" s="26">
         <v>46405</v>
@@ -5058,18 +5069,18 @@
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O23" s="23"/>
       <c r="P23" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q23" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R23" s="23"/>
       <c r="S23" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T23" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5079,7 +5090,7 @@
         <v>25</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W23" s="30"/>
       <c r="X23" s="31"/>
@@ -5098,7 +5109,7 @@
       </c>
       <c r="AF23" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AG23" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5108,22 +5119,22 @@
     </row>
     <row r="24" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G24" s="26">
         <v>46426</v>
@@ -5148,18 +5159,18 @@
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O24" s="23"/>
       <c r="P24" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q24" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R24" s="23"/>
       <c r="S24" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T24" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5169,7 +5180,7 @@
         <v>25</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W24" s="30"/>
       <c r="X24" s="31"/>
@@ -5188,7 +5199,7 @@
       </c>
       <c r="AF24" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AG24" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5198,22 +5209,22 @@
     </row>
     <row r="25" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G25" s="26">
         <v>46440</v>
@@ -5238,18 +5249,18 @@
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O25" s="23"/>
       <c r="P25" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q25" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R25" s="23"/>
       <c r="S25" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T25" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5259,7 +5270,7 @@
         <v>25</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W25" s="30"/>
       <c r="X25" s="31"/>
@@ -5278,7 +5289,7 @@
       </c>
       <c r="AF25" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AG25" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5288,22 +5299,22 @@
     </row>
     <row r="26" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G26" s="26">
         <v>46454</v>
@@ -5328,18 +5339,18 @@
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q26" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R26" s="23"/>
       <c r="S26" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T26" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5349,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W26" s="30"/>
       <c r="X26" s="31"/>
@@ -5368,7 +5379,7 @@
       </c>
       <c r="AF26" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG26" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5378,22 +5389,22 @@
     </row>
     <row r="27" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G27" s="26">
         <v>46468</v>
@@ -5418,18 +5429,18 @@
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O27" s="23"/>
       <c r="P27" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q27" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R27" s="23"/>
       <c r="S27" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T27" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5439,7 +5450,7 @@
         <v>25</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W27" s="30"/>
       <c r="X27" s="31"/>
@@ -5458,7 +5469,7 @@
       </c>
       <c r="AF27" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="AG27" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5468,22 +5479,22 @@
     </row>
     <row r="28" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G28" s="26">
         <v>46482</v>
@@ -5508,18 +5519,18 @@
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O28" s="23"/>
       <c r="P28" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q28" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R28" s="23"/>
       <c r="S28" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T28" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5529,7 +5540,7 @@
         <v>25</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W28" s="30"/>
       <c r="X28" s="31"/>
@@ -5548,7 +5559,7 @@
       </c>
       <c r="AF28" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG28" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5558,22 +5569,22 @@
     </row>
     <row r="29" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G29" s="26">
         <v>46496</v>
@@ -5598,18 +5609,18 @@
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O29" s="23"/>
       <c r="P29" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q29" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R29" s="23"/>
       <c r="S29" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T29" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5619,7 +5630,7 @@
         <v>25</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W29" s="30"/>
       <c r="X29" s="31"/>
@@ -5638,7 +5649,7 @@
       </c>
       <c r="AF29" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG29" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5648,22 +5659,22 @@
     </row>
     <row r="30" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G30" s="26">
         <v>46510</v>
@@ -5688,18 +5699,18 @@
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O30" s="23"/>
       <c r="P30" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q30" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R30" s="23"/>
       <c r="S30" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T30" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5709,7 +5720,7 @@
         <v>25</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W30" s="30"/>
       <c r="X30" s="31"/>
@@ -5728,7 +5739,7 @@
       </c>
       <c r="AF30" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG30" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5738,22 +5749,22 @@
     </row>
     <row r="31" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G31" s="26">
         <v>46531</v>
@@ -5778,18 +5789,18 @@
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q31" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R31" s="23"/>
       <c r="S31" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T31" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5799,7 +5810,7 @@
         <v>25</v>
       </c>
       <c r="V31" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W31" s="30"/>
       <c r="X31" s="31"/>
@@ -5818,7 +5829,7 @@
       </c>
       <c r="AF31" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG31" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5828,22 +5839,22 @@
     </row>
     <row r="32" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G32" s="26">
         <v>46545</v>
@@ -5868,18 +5879,18 @@
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O32" s="23"/>
       <c r="P32" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q32" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R32" s="23"/>
       <c r="S32" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T32" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5889,7 +5900,7 @@
         <v>25</v>
       </c>
       <c r="V32" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W32" s="30"/>
       <c r="X32" s="31"/>
@@ -5908,7 +5919,7 @@
       </c>
       <c r="AF32" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AG32" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5918,22 +5929,22 @@
     </row>
     <row r="33" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G33" s="26">
         <v>46559</v>
@@ -5958,18 +5969,18 @@
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="24" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O33" s="23"/>
       <c r="P33" s="23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q33" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R33" s="23"/>
       <c r="S33" s="29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T33" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5979,7 +5990,7 @@
         <v>25</v>
       </c>
       <c r="V33" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W33" s="30"/>
       <c r="X33" s="31"/>
@@ -5998,7 +6009,7 @@
       </c>
       <c r="AF33" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG33" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6008,19 +6019,19 @@
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>18</v>
@@ -6048,20 +6059,20 @@
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O34" s="23"/>
       <c r="P34" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q34" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S34" s="29" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="T34" s="28" t="str">
         <f t="shared" ref="T34:T65" si="11">IF(TRIM(S34)="","Missing","Published")</f>
@@ -6071,14 +6082,18 @@
         <v>25</v>
       </c>
       <c r="V34" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W34" s="30"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="32" t="str">
+      <c r="X34" s="31">
+        <v>1221</v>
+      </c>
+      <c r="Y34" s="31">
+        <v>746</v>
+      </c>
+      <c r="Z34" s="32">
         <f t="shared" ref="Z34:Z65" si="12">IF(N(X34)&gt;0,N(Y34)/X34,"")</f>
-        <v/>
+        <v>0.61097461097461092</v>
       </c>
       <c r="AA34" s="33"/>
       <c r="AB34" s="34"/>
@@ -6092,29 +6107,28 @@
         <f t="shared" ref="AF34:AF65" ca="1" si="14">IF(G34="","",IF(H34&lt;TODAY(),"",G34-TODAY()))</f>
         <v/>
       </c>
-      <c r="AG34" s="28" t="str">
-        <f t="shared" ref="AG34:AG65" ca="1" si="15">IF(AND(AE34="Past",U34&lt;&gt;"Delivered",U34&lt;&gt;"Cancelled",U34&lt;&gt;"Postponed"),"Update status",IF(AND(T34="Missing",OR(AE34="In progress",AE34="Next 14 days")),"Add link",IF(AND(AE34="Next 14 days",V34&lt;&gt;"Published"),"Announce","")))</f>
-        <v>Update status</v>
+      <c r="AG34" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="AH34" s="28" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>18</v>
@@ -6142,20 +6156,20 @@
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O35" s="23"/>
       <c r="P35" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q35" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="T35" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6165,14 +6179,18 @@
         <v>25</v>
       </c>
       <c r="V35" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W35" s="30"/>
-      <c r="X35" s="31"/>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="32" t="str">
+      <c r="X35" s="31">
+        <v>110</v>
+      </c>
+      <c r="Y35" s="31">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="32">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA35" s="33"/>
       <c r="AB35" s="34"/>
@@ -6184,31 +6202,31 @@
       </c>
       <c r="AF35" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG35" s="28" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="AG35:AG65" ca="1" si="15">IF(AND(AE35="Past",U35&lt;&gt;"Delivered",U35&lt;&gt;"Cancelled",U35&lt;&gt;"Postponed"),"Update status",IF(AND(T35="Missing",OR(AE35="In progress",AE35="Next 14 days")),"Add link",IF(AND(AE35="Next 14 days",V35&lt;&gt;"Published"),"Announce","")))</f>
         <v/>
       </c>
       <c r="AH35" s="28" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>18</v>
@@ -6236,20 +6254,20 @@
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O36" s="23"/>
       <c r="P36" s="23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q36" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="T36" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6259,7 +6277,7 @@
         <v>25</v>
       </c>
       <c r="V36" s="30" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="W36" s="30"/>
       <c r="X36" s="31"/>
@@ -6278,31 +6296,28 @@
       </c>
       <c r="AF36" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>5</v>
-      </c>
-      <c r="AG36" s="28" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AG36" s="28"/>
       <c r="AH36" s="28" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>18</v>
@@ -6330,20 +6345,20 @@
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O37" s="23"/>
       <c r="P37" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q37" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R37" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S37" s="29" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="T37" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6353,7 +6368,7 @@
         <v>25</v>
       </c>
       <c r="V37" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W37" s="30"/>
       <c r="X37" s="31"/>
@@ -6372,31 +6387,31 @@
       </c>
       <c r="AF37" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG37" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v>Announce</v>
       </c>
       <c r="AH37" s="28" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" s="23" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>18</v>
@@ -6424,17 +6439,17 @@
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O38" s="23"/>
       <c r="P38" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q38" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S38" s="30"/>
       <c r="T38" s="28" t="str">
@@ -6445,7 +6460,7 @@
         <v>23</v>
       </c>
       <c r="V38" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W38" s="30"/>
       <c r="X38" s="31"/>
@@ -6464,31 +6479,31 @@
       </c>
       <c r="AF38" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AG38" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH38" s="28" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>18</v>
@@ -6516,20 +6531,20 @@
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O39" s="23"/>
       <c r="P39" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q39" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="T39" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6539,7 +6554,7 @@
         <v>25</v>
       </c>
       <c r="V39" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W39" s="30"/>
       <c r="X39" s="31"/>
@@ -6558,31 +6573,31 @@
       </c>
       <c r="AF39" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG39" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH39" s="28" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>18</v>
@@ -6610,20 +6625,20 @@
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="24" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="O40" s="23"/>
       <c r="P40" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q40" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="T40" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6633,7 +6648,7 @@
         <v>25</v>
       </c>
       <c r="V40" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W40" s="30"/>
       <c r="X40" s="31"/>
@@ -6652,31 +6667,31 @@
       </c>
       <c r="AF40" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG40" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH40" s="28" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>18</v>
@@ -6704,20 +6719,20 @@
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="24" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O41" s="23"/>
       <c r="P41" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q41" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R41" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S41" s="29" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="T41" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6727,7 +6742,7 @@
         <v>25</v>
       </c>
       <c r="V41" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W41" s="30"/>
       <c r="X41" s="31"/>
@@ -6746,31 +6761,31 @@
       </c>
       <c r="AF41" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AG41" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH41" s="28" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F42" s="23" t="s">
         <v>18</v>
@@ -6798,17 +6813,17 @@
       </c>
       <c r="M42" s="23"/>
       <c r="N42" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O42" s="23"/>
       <c r="P42" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q42" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S42" s="30"/>
       <c r="T42" s="28" t="str">
@@ -6819,7 +6834,7 @@
         <v>23</v>
       </c>
       <c r="V42" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W42" s="30"/>
       <c r="X42" s="31"/>
@@ -6834,35 +6849,35 @@
       <c r="AD42" s="34"/>
       <c r="AE42" s="28" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Later</v>
+        <v>Next 45 days</v>
       </c>
       <c r="AF42" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AG42" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH42" s="28" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>18</v>
@@ -6890,20 +6905,20 @@
       </c>
       <c r="M43" s="23"/>
       <c r="N43" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O43" s="23"/>
       <c r="P43" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q43" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S43" s="29" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="T43" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6913,7 +6928,7 @@
         <v>25</v>
       </c>
       <c r="V43" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W43" s="30"/>
       <c r="X43" s="31"/>
@@ -6932,31 +6947,31 @@
       </c>
       <c r="AF43" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG43" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH43" s="28" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" s="23" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>18</v>
@@ -6984,20 +6999,20 @@
       </c>
       <c r="M44" s="23"/>
       <c r="N44" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O44" s="23"/>
       <c r="P44" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q44" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R44" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S44" s="29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="T44" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7007,7 +7022,7 @@
         <v>25</v>
       </c>
       <c r="V44" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W44" s="30"/>
       <c r="X44" s="31"/>
@@ -7026,31 +7041,31 @@
       </c>
       <c r="AF44" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AG44" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH44" s="28" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A45" s="23" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B45" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>18</v>
@@ -7078,20 +7093,20 @@
       </c>
       <c r="M45" s="23"/>
       <c r="N45" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O45" s="23"/>
       <c r="P45" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q45" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R45" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S45" s="29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="T45" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7101,7 +7116,7 @@
         <v>25</v>
       </c>
       <c r="V45" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W45" s="30"/>
       <c r="X45" s="31"/>
@@ -7120,31 +7135,31 @@
       </c>
       <c r="AF45" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AG45" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH45" s="28" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A46" s="23" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>18</v>
@@ -7172,20 +7187,20 @@
       </c>
       <c r="M46" s="23"/>
       <c r="N46" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O46" s="23"/>
       <c r="P46" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q46" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R46" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S46" s="29" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="T46" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7195,7 +7210,7 @@
         <v>25</v>
       </c>
       <c r="V46" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W46" s="30"/>
       <c r="X46" s="31"/>
@@ -7214,31 +7229,31 @@
       </c>
       <c r="AF46" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AG46" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH46" s="28" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>18</v>
@@ -7266,17 +7281,17 @@
       </c>
       <c r="M47" s="23"/>
       <c r="N47" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O47" s="23"/>
       <c r="P47" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q47" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R47" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S47" s="30"/>
       <c r="T47" s="28" t="str">
@@ -7287,7 +7302,7 @@
         <v>23</v>
       </c>
       <c r="V47" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W47" s="30"/>
       <c r="X47" s="31"/>
@@ -7306,31 +7321,31 @@
       </c>
       <c r="AF47" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AG47" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH47" s="28" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>18</v>
@@ -7358,17 +7373,17 @@
       </c>
       <c r="M48" s="23"/>
       <c r="N48" s="24" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O48" s="23"/>
       <c r="P48" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q48" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R48" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S48" s="30"/>
       <c r="T48" s="28" t="str">
@@ -7379,7 +7394,7 @@
         <v>23</v>
       </c>
       <c r="V48" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W48" s="30"/>
       <c r="X48" s="31"/>
@@ -7398,31 +7413,31 @@
       </c>
       <c r="AF48" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AG48" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH48" s="28" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A49" s="23" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>18</v>
@@ -7450,17 +7465,17 @@
       </c>
       <c r="M49" s="23"/>
       <c r="N49" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O49" s="23"/>
       <c r="P49" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q49" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S49" s="30"/>
       <c r="T49" s="28" t="str">
@@ -7471,7 +7486,7 @@
         <v>23</v>
       </c>
       <c r="V49" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W49" s="30"/>
       <c r="X49" s="31"/>
@@ -7490,31 +7505,31 @@
       </c>
       <c r="AF49" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AG49" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH49" s="28" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>18</v>
@@ -7542,17 +7557,17 @@
       </c>
       <c r="M50" s="23"/>
       <c r="N50" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O50" s="23"/>
       <c r="P50" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q50" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S50" s="30"/>
       <c r="T50" s="28" t="str">
@@ -7563,7 +7578,7 @@
         <v>23</v>
       </c>
       <c r="V50" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W50" s="30"/>
       <c r="X50" s="31"/>
@@ -7582,31 +7597,31 @@
       </c>
       <c r="AF50" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AG50" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH50" s="28" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>18</v>
@@ -7634,17 +7649,17 @@
       </c>
       <c r="M51" s="23"/>
       <c r="N51" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O51" s="23"/>
       <c r="P51" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q51" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R51" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S51" s="30"/>
       <c r="T51" s="28" t="str">
@@ -7655,7 +7670,7 @@
         <v>23</v>
       </c>
       <c r="V51" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W51" s="30"/>
       <c r="X51" s="31"/>
@@ -7674,31 +7689,31 @@
       </c>
       <c r="AF51" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AG51" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH51" s="28" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52" s="23" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>18</v>
@@ -7726,17 +7741,17 @@
       </c>
       <c r="M52" s="23"/>
       <c r="N52" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O52" s="23"/>
       <c r="P52" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q52" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R52" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S52" s="30"/>
       <c r="T52" s="28" t="str">
@@ -7747,7 +7762,7 @@
         <v>23</v>
       </c>
       <c r="V52" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W52" s="30"/>
       <c r="X52" s="31"/>
@@ -7766,31 +7781,31 @@
       </c>
       <c r="AF52" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="AG52" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH52" s="28" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B53" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F53" s="23" t="s">
         <v>18</v>
@@ -7818,17 +7833,17 @@
       </c>
       <c r="M53" s="23"/>
       <c r="N53" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O53" s="23"/>
       <c r="P53" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q53" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R53" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S53" s="30"/>
       <c r="T53" s="28" t="str">
@@ -7839,7 +7854,7 @@
         <v>23</v>
       </c>
       <c r="V53" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W53" s="30"/>
       <c r="X53" s="31"/>
@@ -7858,31 +7873,31 @@
       </c>
       <c r="AF53" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AG53" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH53" s="28" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>18</v>
@@ -7910,17 +7925,17 @@
       </c>
       <c r="M54" s="23"/>
       <c r="N54" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O54" s="23"/>
       <c r="P54" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q54" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R54" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S54" s="30"/>
       <c r="T54" s="28" t="str">
@@ -7931,7 +7946,7 @@
         <v>23</v>
       </c>
       <c r="V54" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W54" s="30"/>
       <c r="X54" s="31"/>
@@ -7950,31 +7965,31 @@
       </c>
       <c r="AF54" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG54" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH54" s="28" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B55" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F55" s="23" t="s">
         <v>18</v>
@@ -8002,17 +8017,17 @@
       </c>
       <c r="M55" s="23"/>
       <c r="N55" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O55" s="23"/>
       <c r="P55" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q55" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R55" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S55" s="30"/>
       <c r="T55" s="28" t="str">
@@ -8023,7 +8038,7 @@
         <v>23</v>
       </c>
       <c r="V55" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W55" s="30"/>
       <c r="X55" s="31"/>
@@ -8042,31 +8057,31 @@
       </c>
       <c r="AF55" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG55" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH55" s="28" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A56" s="23" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B56" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>18</v>
@@ -8094,17 +8109,17 @@
       </c>
       <c r="M56" s="23"/>
       <c r="N56" s="24" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O56" s="23"/>
       <c r="P56" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q56" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R56" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S56" s="30"/>
       <c r="T56" s="28" t="str">
@@ -8115,7 +8130,7 @@
         <v>23</v>
       </c>
       <c r="V56" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W56" s="30"/>
       <c r="X56" s="31"/>
@@ -8134,31 +8149,31 @@
       </c>
       <c r="AF56" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="AG56" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH56" s="28" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F57" s="23" t="s">
         <v>18</v>
@@ -8186,17 +8201,17 @@
       </c>
       <c r="M57" s="23"/>
       <c r="N57" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O57" s="23"/>
       <c r="P57" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q57" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S57" s="30"/>
       <c r="T57" s="28" t="str">
@@ -8207,7 +8222,7 @@
         <v>23</v>
       </c>
       <c r="V57" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W57" s="30"/>
       <c r="X57" s="31"/>
@@ -8226,31 +8241,31 @@
       </c>
       <c r="AF57" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AG57" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH57" s="28" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F58" s="23" t="s">
         <v>18</v>
@@ -8278,17 +8293,17 @@
       </c>
       <c r="M58" s="23"/>
       <c r="N58" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O58" s="23"/>
       <c r="P58" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q58" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R58" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S58" s="30"/>
       <c r="T58" s="28" t="str">
@@ -8299,7 +8314,7 @@
         <v>23</v>
       </c>
       <c r="V58" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W58" s="30"/>
       <c r="X58" s="31"/>
@@ -8318,31 +8333,31 @@
       </c>
       <c r="AF58" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG58" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH58" s="28" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B59" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F59" s="23" t="s">
         <v>18</v>
@@ -8370,17 +8385,17 @@
       </c>
       <c r="M59" s="23"/>
       <c r="N59" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O59" s="23"/>
       <c r="P59" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q59" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R59" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S59" s="30"/>
       <c r="T59" s="28" t="str">
@@ -8391,7 +8406,7 @@
         <v>23</v>
       </c>
       <c r="V59" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W59" s="30"/>
       <c r="X59" s="31"/>
@@ -8410,31 +8425,31 @@
       </c>
       <c r="AF59" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG59" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH59" s="28" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A60" s="23" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F60" s="23" t="s">
         <v>18</v>
@@ -8462,17 +8477,17 @@
       </c>
       <c r="M60" s="23"/>
       <c r="N60" s="24" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="O60" s="23"/>
       <c r="P60" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q60" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R60" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S60" s="30"/>
       <c r="T60" s="28" t="str">
@@ -8483,7 +8498,7 @@
         <v>23</v>
       </c>
       <c r="V60" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W60" s="30"/>
       <c r="X60" s="31"/>
@@ -8502,31 +8517,31 @@
       </c>
       <c r="AF60" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG60" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH60" s="28" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B61" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F61" s="23" t="s">
         <v>18</v>
@@ -8554,17 +8569,17 @@
       </c>
       <c r="M61" s="23"/>
       <c r="N61" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O61" s="23"/>
       <c r="P61" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q61" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S61" s="30"/>
       <c r="T61" s="28" t="str">
@@ -8575,7 +8590,7 @@
         <v>23</v>
       </c>
       <c r="V61" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W61" s="30"/>
       <c r="X61" s="31"/>
@@ -8594,31 +8609,31 @@
       </c>
       <c r="AF61" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG61" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH61" s="28" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B62" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F62" s="23" t="s">
         <v>18</v>
@@ -8646,17 +8661,17 @@
       </c>
       <c r="M62" s="23"/>
       <c r="N62" s="24" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O62" s="23"/>
       <c r="P62" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q62" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="S62" s="30"/>
       <c r="T62" s="28" t="str">
@@ -8667,7 +8682,7 @@
         <v>23</v>
       </c>
       <c r="V62" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W62" s="30"/>
       <c r="X62" s="31"/>
@@ -8686,31 +8701,31 @@
       </c>
       <c r="AF62" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AG62" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH62" s="28" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B63" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F63" s="23" t="s">
         <v>18</v>
@@ -8738,17 +8753,17 @@
       </c>
       <c r="M63" s="23"/>
       <c r="N63" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O63" s="23"/>
       <c r="P63" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q63" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S63" s="30"/>
       <c r="T63" s="28" t="str">
@@ -8759,7 +8774,7 @@
         <v>23</v>
       </c>
       <c r="V63" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W63" s="30"/>
       <c r="X63" s="31"/>
@@ -8778,31 +8793,31 @@
       </c>
       <c r="AF63" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AG63" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH63" s="28" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A64" s="23" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F64" s="23" t="s">
         <v>18</v>
@@ -8830,17 +8845,17 @@
       </c>
       <c r="M64" s="23"/>
       <c r="N64" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O64" s="23"/>
       <c r="P64" s="23" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Q64" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R64" s="23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="S64" s="30"/>
       <c r="T64" s="28" t="str">
@@ -8851,7 +8866,7 @@
         <v>23</v>
       </c>
       <c r="V64" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W64" s="30"/>
       <c r="X64" s="31"/>
@@ -8870,31 +8885,31 @@
       </c>
       <c r="AF64" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG64" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH64" s="28" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>18</v>
@@ -8922,17 +8937,17 @@
       </c>
       <c r="M65" s="23"/>
       <c r="N65" s="24" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O65" s="23"/>
       <c r="P65" s="23" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R65" s="23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="S65" s="30"/>
       <c r="T65" s="28" t="str">
@@ -8943,7 +8958,7 @@
         <v>23</v>
       </c>
       <c r="V65" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W65" s="30"/>
       <c r="X65" s="31"/>
@@ -8962,34 +8977,34 @@
       </c>
       <c r="AF65" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AG65" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH65" s="28" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G66" s="26">
         <v>46321</v>
@@ -9014,12 +9029,12 @@
       </c>
       <c r="M66" s="23"/>
       <c r="N66" s="24" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O66" s="23"/>
       <c r="P66" s="23"/>
       <c r="Q66" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R66" s="23"/>
       <c r="S66" s="30"/>
@@ -9031,7 +9046,7 @@
         <v>23</v>
       </c>
       <c r="V66" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W66" s="30"/>
       <c r="X66" s="31"/>
@@ -9050,34 +9065,34 @@
       </c>
       <c r="AF66" s="28">
         <f t="shared" ref="AF66:AF81" ca="1" si="22">IF(G66="","",IF(H66&lt;TODAY(),"",G66-TODAY()))</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG66" s="28" t="str">
         <f t="shared" ref="AG66:AG81" ca="1" si="23">IF(AND(AE66="Past",U66&lt;&gt;"Delivered",U66&lt;&gt;"Cancelled",U66&lt;&gt;"Postponed"),"Update status",IF(AND(T66="Missing",OR(AE66="In progress",AE66="Next 14 days")),"Add link",IF(AND(AE66="Next 14 days",V66&lt;&gt;"Published"),"Announce","")))</f>
         <v/>
       </c>
       <c r="AH66" s="28" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A67" s="23" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B67" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C67" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="F67" s="23" t="s">
         <v>386</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>382</v>
       </c>
       <c r="G67" s="26">
         <v>46419</v>
@@ -9102,12 +9117,12 @@
       </c>
       <c r="M67" s="23"/>
       <c r="N67" s="24" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O67" s="23"/>
       <c r="P67" s="23"/>
       <c r="Q67" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R67" s="23"/>
       <c r="S67" s="30"/>
@@ -9119,7 +9134,7 @@
         <v>23</v>
       </c>
       <c r="V67" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W67" s="30"/>
       <c r="X67" s="31"/>
@@ -9138,34 +9153,34 @@
       </c>
       <c r="AF67" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AG67" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH67" s="28" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E68" s="25" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G68" s="26">
         <v>46419</v>
@@ -9174,7 +9189,7 @@
         <v>46446</v>
       </c>
       <c r="I68" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J68" s="27">
         <f t="shared" si="16"/>
@@ -9190,12 +9205,12 @@
       </c>
       <c r="M68" s="23"/>
       <c r="N68" s="24" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="O68" s="23"/>
       <c r="P68" s="23"/>
       <c r="Q68" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R68" s="23"/>
       <c r="S68" s="30"/>
@@ -9207,7 +9222,7 @@
         <v>23</v>
       </c>
       <c r="V68" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W68" s="30"/>
       <c r="X68" s="31"/>
@@ -9226,34 +9241,34 @@
       </c>
       <c r="AF68" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AG68" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH68" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C69" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="F69" s="23" t="s">
         <v>386</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>382</v>
       </c>
       <c r="G69" s="26">
         <v>46497</v>
@@ -9278,12 +9293,12 @@
       </c>
       <c r="M69" s="23"/>
       <c r="N69" s="24" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O69" s="23"/>
       <c r="P69" s="23"/>
       <c r="Q69" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R69" s="23"/>
       <c r="S69" s="30"/>
@@ -9295,7 +9310,7 @@
         <v>23</v>
       </c>
       <c r="V69" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W69" s="30"/>
       <c r="X69" s="31"/>
@@ -9314,34 +9329,34 @@
       </c>
       <c r="AF69" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AG69" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH69" s="28" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A70" s="23" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E70" s="25" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G70" s="26">
         <v>46357</v>
@@ -9350,7 +9365,7 @@
         <v>46387</v>
       </c>
       <c r="I70" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J70" s="27">
         <f t="shared" si="16"/>
@@ -9368,10 +9383,10 @@
       <c r="N70" s="24"/>
       <c r="O70" s="23"/>
       <c r="P70" s="23" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q70" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R70" s="23"/>
       <c r="S70" s="30"/>
@@ -9383,7 +9398,7 @@
         <v>23</v>
       </c>
       <c r="V70" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W70" s="30"/>
       <c r="X70" s="31"/>
@@ -9402,34 +9417,34 @@
       </c>
       <c r="AF70" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AG70" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH70" s="28" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="71" spans="1:34" ht="25.5" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G71" s="26">
         <v>46357</v>
@@ -9438,7 +9453,7 @@
         <v>46387</v>
       </c>
       <c r="I71" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J71" s="27">
         <f t="shared" si="16"/>
@@ -9456,10 +9471,10 @@
       <c r="N71" s="24"/>
       <c r="O71" s="23"/>
       <c r="P71" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q71" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R71" s="23"/>
       <c r="S71" s="30"/>
@@ -9471,7 +9486,7 @@
         <v>23</v>
       </c>
       <c r="V71" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W71" s="30"/>
       <c r="X71" s="31"/>
@@ -9490,34 +9505,34 @@
       </c>
       <c r="AF71" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AG71" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH71" s="28" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A72" s="23" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E72" s="25" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G72" s="26">
         <v>46388</v>
@@ -9526,7 +9541,7 @@
         <v>46418</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J72" s="27">
         <f t="shared" si="16"/>
@@ -9544,10 +9559,10 @@
       <c r="N72" s="24"/>
       <c r="O72" s="23"/>
       <c r="P72" s="23" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R72" s="23"/>
       <c r="S72" s="30"/>
@@ -9559,7 +9574,7 @@
         <v>23</v>
       </c>
       <c r="V72" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W72" s="30"/>
       <c r="X72" s="31"/>
@@ -9578,34 +9593,34 @@
       </c>
       <c r="AF72" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AG72" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH72" s="28" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A73" s="23" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E73" s="25" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G73" s="26">
         <v>46419</v>
@@ -9614,7 +9629,7 @@
         <v>46446</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J73" s="27">
         <f t="shared" si="16"/>
@@ -9632,10 +9647,10 @@
       <c r="N73" s="24"/>
       <c r="O73" s="23"/>
       <c r="P73" s="23" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="Q73" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R73" s="23"/>
       <c r="S73" s="30"/>
@@ -9647,7 +9662,7 @@
         <v>23</v>
       </c>
       <c r="V73" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W73" s="30"/>
       <c r="X73" s="31"/>
@@ -9666,34 +9681,34 @@
       </c>
       <c r="AF73" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AG73" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH73" s="28" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A74" s="23" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E74" s="25" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G74" s="26">
         <v>46447</v>
@@ -9702,7 +9717,7 @@
         <v>46477</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J74" s="27">
         <f t="shared" si="16"/>
@@ -9720,10 +9735,10 @@
       <c r="N74" s="24"/>
       <c r="O74" s="23"/>
       <c r="P74" s="23" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="Q74" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R74" s="23"/>
       <c r="S74" s="30"/>
@@ -9735,7 +9750,7 @@
         <v>23</v>
       </c>
       <c r="V74" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W74" s="30"/>
       <c r="X74" s="31"/>
@@ -9754,34 +9769,34 @@
       </c>
       <c r="AF74" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG74" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH74" s="28" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A75" s="23" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E75" s="25" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G75" s="26">
         <v>46447</v>
@@ -9790,7 +9805,7 @@
         <v>46477</v>
       </c>
       <c r="I75" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J75" s="27">
         <f t="shared" si="16"/>
@@ -9808,10 +9823,10 @@
       <c r="N75" s="24"/>
       <c r="O75" s="23"/>
       <c r="P75" s="23" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="Q75" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R75" s="23"/>
       <c r="S75" s="30"/>
@@ -9823,7 +9838,7 @@
         <v>23</v>
       </c>
       <c r="V75" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W75" s="30"/>
       <c r="X75" s="31"/>
@@ -9842,34 +9857,34 @@
       </c>
       <c r="AF75" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG75" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH75" s="28" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A76" s="23" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B76" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E76" s="25" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G76" s="26">
         <v>46478</v>
@@ -9878,7 +9893,7 @@
         <v>46507</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J76" s="27">
         <f t="shared" si="16"/>
@@ -9896,10 +9911,10 @@
       <c r="N76" s="24"/>
       <c r="O76" s="23"/>
       <c r="P76" s="23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R76" s="23"/>
       <c r="S76" s="30"/>
@@ -9911,7 +9926,7 @@
         <v>23</v>
       </c>
       <c r="V76" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W76" s="30"/>
       <c r="X76" s="31"/>
@@ -9930,34 +9945,34 @@
       </c>
       <c r="AF76" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG76" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH76" s="28" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A77" s="23" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B77" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G77" s="26">
         <v>46478</v>
@@ -9966,7 +9981,7 @@
         <v>46507</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J77" s="27">
         <f t="shared" si="16"/>
@@ -9984,10 +9999,10 @@
       <c r="N77" s="24"/>
       <c r="O77" s="23"/>
       <c r="P77" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q77" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R77" s="23"/>
       <c r="S77" s="30"/>
@@ -9999,7 +10014,7 @@
         <v>23</v>
       </c>
       <c r="V77" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W77" s="30"/>
       <c r="X77" s="31"/>
@@ -10018,34 +10033,34 @@
       </c>
       <c r="AF77" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG77" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH77" s="28" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" s="23" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G78" s="26">
         <v>46478</v>
@@ -10054,7 +10069,7 @@
         <v>46507</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J78" s="27">
         <f t="shared" si="16"/>
@@ -10072,10 +10087,10 @@
       <c r="N78" s="24"/>
       <c r="O78" s="23"/>
       <c r="P78" s="23" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R78" s="23"/>
       <c r="S78" s="30"/>
@@ -10087,7 +10102,7 @@
         <v>23</v>
       </c>
       <c r="V78" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W78" s="30"/>
       <c r="X78" s="31"/>
@@ -10106,34 +10121,34 @@
       </c>
       <c r="AF78" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AG78" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH78" s="28" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A79" s="23" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G79" s="26">
         <v>46489</v>
@@ -10161,7 +10176,7 @@
       <c r="O79" s="23"/>
       <c r="P79" s="23"/>
       <c r="Q79" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R79" s="23"/>
       <c r="S79" s="30"/>
@@ -10173,7 +10188,7 @@
         <v>23</v>
       </c>
       <c r="V79" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W79" s="30"/>
       <c r="X79" s="31"/>
@@ -10192,34 +10207,34 @@
       </c>
       <c r="AF79" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG79" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH79" s="28" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A80" s="23" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G80" s="26">
         <v>46508</v>
@@ -10228,7 +10243,7 @@
         <v>46538</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J80" s="27">
         <f t="shared" si="16"/>
@@ -10246,10 +10261,10 @@
       <c r="N80" s="24"/>
       <c r="O80" s="23"/>
       <c r="P80" s="23" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R80" s="23"/>
       <c r="S80" s="30"/>
@@ -10261,7 +10276,7 @@
         <v>23</v>
       </c>
       <c r="V80" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W80" s="30"/>
       <c r="X80" s="31"/>
@@ -10280,34 +10295,34 @@
       </c>
       <c r="AF80" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG80" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH80" s="28" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="23" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B81" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G81" s="26">
         <v>46508</v>
@@ -10316,7 +10331,7 @@
         <v>46538</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J81" s="27">
         <f t="shared" si="16"/>
@@ -10334,10 +10349,10 @@
       <c r="N81" s="24"/>
       <c r="O81" s="23"/>
       <c r="P81" s="23" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="Q81" s="23" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="R81" s="23"/>
       <c r="S81" s="30"/>
@@ -10349,7 +10364,7 @@
         <v>23</v>
       </c>
       <c r="V81" s="30" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="W81" s="30"/>
       <c r="X81" s="31"/>
@@ -10368,14 +10383,14 @@
       </c>
       <c r="AF81" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG81" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH81" s="28" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -10580,16 +10595,16 @@
         <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D2" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10600,16 +10615,16 @@
         <v>24</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10620,16 +10635,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10640,10 +10655,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10654,7 +10669,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>469</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -10681,22 +10696,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F1" s="36" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10707,13 +10722,13 @@
         <v>46291</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F11" si="0">B2-A2+1</f>
@@ -10728,13 +10743,13 @@
         <v>46354</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" si="0"/>
@@ -10749,13 +10764,13 @@
         <v>46395</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
@@ -10770,13 +10785,13 @@
         <v>46403</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="0"/>
@@ -10791,13 +10806,13 @@
         <v>46408</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="0"/>
@@ -10812,13 +10827,13 @@
         <v>46422</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>486</v>
       </c>
-      <c r="D7" s="39" t="s">
-        <v>483</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="0"/>
@@ -10833,13 +10848,13 @@
         <v>46440</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="0"/>
@@ -10854,13 +10869,13 @@
         <v>46459</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
@@ -10875,13 +10890,13 @@
         <v>46529</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
@@ -10896,13 +10911,13 @@
         <v>46534</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="0"/>
@@ -10911,7 +10926,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.8 Events Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E833A5F-2A8A-44B7-8DB8-62EB9CEB2AC9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E7111A5E-DF79-4BCD-AE42-443509611752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA3CEE6-345B-404F-9DCF-0172C70C029D}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="J7" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B7)</f>
-        <v>552</v>
+        <v>1095</v>
       </c>
       <c r="K7" s="8">
         <f>SUMIFS(Events!$Y$2:$Y$400,Events!$B$2:$B$400,$B7)</f>
-        <v>251</v>
+        <v>677</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" ref="L7:L12" si="0">IF(J7&gt;0,K7/J7,"-")</f>
-        <v>0.45471014492753625</v>
+        <v>0.61826484018264838</v>
       </c>
       <c r="M7" s="9" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0",Events!$B$2:$B$400,$B7),"-")</f>
@@ -2543,15 +2543,15 @@
       </c>
       <c r="J9" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B9)</f>
-        <v>1331</v>
+        <v>1447</v>
       </c>
       <c r="K9" s="8">
         <f>SUMIFS(Events!$Y$2:$Y$400,Events!$B$2:$B$400,$B9)</f>
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>0.56048084147257704</v>
+        <v>0.54111955770559783</v>
       </c>
       <c r="M9" s="9" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0",Events!$B$2:$B$400,$B9),"-")</f>
@@ -2702,15 +2702,15 @@
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
-        <v>1883</v>
+        <v>2542</v>
       </c>
       <c r="K12" s="12">
         <f>SUM(Events!$Y$2:$Y$400)</f>
-        <v>997</v>
+        <v>1460</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="0"/>
-        <v>0.52947424322889003</v>
+        <v>0.57435090479937057</v>
       </c>
       <c r="M12" s="13" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0"),"-")</f>
@@ -2954,8 +2954,8 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
-    <col min="4" max="4" width="67.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="67.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
@@ -2969,8 +2969,9 @@
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="34" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="23" width="16" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="11" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
@@ -3161,11 +3162,15 @@
         <v>100</v>
       </c>
       <c r="W2" s="30"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="32" t="str">
+      <c r="X2" s="31">
+        <v>543</v>
+      </c>
+      <c r="Y2" s="31">
+        <v>426</v>
+      </c>
+      <c r="Z2" s="32">
         <f t="shared" ref="Z2:Z33" si="4">IF(N(X2)&gt;0,N(Y2)/X2,"")</f>
-        <v/>
+        <v>0.78453038674033149</v>
       </c>
       <c r="AA2" s="33"/>
       <c r="AB2" s="34"/>
@@ -3255,11 +3260,15 @@
         <v>100</v>
       </c>
       <c r="W3" s="30"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="32" t="str">
+      <c r="X3" s="31">
+        <v>116</v>
+      </c>
+      <c r="Y3" s="31">
+        <v>37</v>
+      </c>
+      <c r="Z3" s="32">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.31896551724137934</v>
       </c>
       <c r="AA3" s="33"/>
       <c r="AB3" s="34"/>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.8 Events Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E7111A5E-DF79-4BCD-AE42-443509611752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA3CEE6-345B-404F-9DCF-0172C70C029D}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5E3910-BC54-4FFC-82C5-0A6DD4AD617B}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="500">
   <si>
     <t>AY26-27 Classera Plans | Events Tracker</t>
   </si>
@@ -394,12 +394,6 @@
     <t>Intel SFI</t>
   </si>
   <si>
-    <t>Intel Skills for Innovation (SFI) Webinar 1 — AI Professional Development</t>
-  </si>
-  <si>
-    <t>Intel Skills for Innovation — التطوير المهني في الذكاء الاصطناعي (1)</t>
-  </si>
-  <si>
     <t>Intel</t>
   </si>
   <si>
@@ -1541,6 +1535,15 @@
   </si>
   <si>
     <t>Source: plans.classera.com Full Calendar (KSA and Egypt school calendars). No sessions are scheduled inside these periods.</t>
+  </si>
+  <si>
+    <t>Creative Tech: Helping Students Tell Stories Through AI</t>
+  </si>
+  <si>
+    <t>التقنية الإبداعية: مساعدة الطلاب على سرد القصص من خلال الذكاء الاصطناعي</t>
+  </si>
+  <si>
+    <t>https://sh.classera.com/sfiw1s</t>
   </si>
 </sst>
 </file>
@@ -2359,7 +2362,7 @@
       </c>
       <c r="C4" s="4">
         <f ca="1">TODAY()</f>
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2425,11 +2428,11 @@
       </c>
       <c r="G7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Published")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
         <f>COUNTIFS(Events!$B$2:$B$400,$B7,Events!$U$2:$U$400,"Delivered")</f>
@@ -2490,15 +2493,15 @@
       </c>
       <c r="J8" s="8">
         <f>SUMIFS(Events!$X$2:$X$400,Events!$B$2:$B$400,$B8)</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K8" s="8">
         <f>SUMIFS(Events!$Y$2:$Y$400,Events!$B$2:$B$400,$B8)</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="9" t="str">
+        <v>76</v>
+      </c>
+      <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>-</v>
+        <v>0.74509803921568629</v>
       </c>
       <c r="M8" s="9" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0",Events!$B$2:$B$400,$B8),"-")</f>
@@ -2559,7 +2562,7 @@
       </c>
       <c r="N9" s="7">
         <f ca="1">COUNTIFS(Events!$B$2:$B$400,$B9,Events!$AG$2:$AG$400,"?*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -2690,11 +2693,11 @@
       </c>
       <c r="G12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$T$2:$T$400,"Published")</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$T$2:$T$400,"Missing",Events!$A$2:$A$400,"&lt;&gt;")</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="11">
         <f>COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$U$2:$U$400,"Delivered")</f>
@@ -2702,15 +2705,15 @@
       </c>
       <c r="J12" s="12">
         <f>SUM(Events!$X$2:$X$400)</f>
-        <v>2542</v>
+        <v>2644</v>
       </c>
       <c r="K12" s="12">
         <f>SUM(Events!$Y$2:$Y$400)</f>
-        <v>1460</v>
+        <v>1536</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="0"/>
-        <v>0.57435090479937057</v>
+        <v>0.58093797276853254</v>
       </c>
       <c r="M12" s="13" t="str">
         <f>IFERROR(AVERAGEIFS(Events!$AA$2:$AA$400,Events!$AA$2:$AA$400,"&gt;0"),"-")</f>
@@ -2718,7 +2721,7 @@
       </c>
       <c r="N12" s="11">
         <f ca="1">COUNTIFS(Events!$A$2:$A$400,"&lt;&gt;",Events!$AG$2:$AG$400,"?*")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
@@ -2756,11 +2759,11 @@
       </c>
       <c r="D16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,D$15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,E$15)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,F$15)</f>
@@ -2810,7 +2813,7 @@
       </c>
       <c r="C22" s="17">
         <f ca="1">COUNTIFS(Events!$AG$2:$AG$400,B22)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>34</v>
@@ -2954,8 +2957,8 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="67.85546875" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="9" width="12" customWidth="1"/>
@@ -2969,9 +2972,8 @@
     <col min="17" max="17" width="11" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="19" max="19" width="34" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="16" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="13" customWidth="1"/>
     <col min="25" max="25" width="11" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
@@ -3343,7 +3345,9 @@
       <c r="Q4" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R4" s="23"/>
+      <c r="R4" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S4" s="29" t="s">
         <v>112</v>
       </c>
@@ -3399,13 +3403,13 @@
         <v>115</v>
       </c>
       <c r="D5" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>116</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>118</v>
       </c>
       <c r="G5" s="26">
         <v>46309</v>
@@ -3432,10 +3436,10 @@
         <v>94</v>
       </c>
       <c r="N5" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P5" s="23" t="s">
         <v>97</v>
@@ -3443,17 +3447,21 @@
       <c r="Q5" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R5" s="23"/>
-      <c r="S5" s="30"/>
+      <c r="R5" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="S5" s="41" t="s">
+        <v>499</v>
+      </c>
       <c r="T5" s="28" t="str">
         <f t="shared" si="3"/>
-        <v>Missing</v>
+        <v>Published</v>
       </c>
       <c r="U5" s="30" t="s">
         <v>24</v>
       </c>
       <c r="V5" s="30" t="s">
-        <v>121</v>
+        <v>466</v>
       </c>
       <c r="W5" s="30"/>
       <c r="X5" s="31"/>
@@ -3472,34 +3480,34 @@
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG5" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Add link</v>
+        <v>Announce</v>
       </c>
       <c r="AH5" s="28" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="F6" s="23" t="s">
         <v>125</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>127</v>
       </c>
       <c r="G6" s="26">
         <v>46323</v>
@@ -3526,7 +3534,7 @@
         <v>94</v>
       </c>
       <c r="N6" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O6" s="23" t="s">
         <v>96</v>
@@ -3537,7 +3545,9 @@
       <c r="Q6" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R6" s="23"/>
+      <c r="R6" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S6" s="30"/>
       <c r="T6" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3547,7 +3557,7 @@
         <v>23</v>
       </c>
       <c r="V6" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W6" s="30"/>
       <c r="X6" s="31"/>
@@ -3566,34 +3576,34 @@
       </c>
       <c r="AF6" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG6" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH6" s="28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D7" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>131</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>133</v>
       </c>
       <c r="G7" s="26">
         <v>46337</v>
@@ -3620,10 +3630,10 @@
         <v>94</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P7" s="23" t="s">
         <v>97</v>
@@ -3631,7 +3641,9 @@
       <c r="Q7" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R7" s="23"/>
+      <c r="R7" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S7" s="30"/>
       <c r="T7" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3641,7 +3653,7 @@
         <v>23</v>
       </c>
       <c r="V7" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W7" s="30"/>
       <c r="X7" s="31"/>
@@ -3660,19 +3672,19 @@
       </c>
       <c r="AF7" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AG7" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH7" s="28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>16</v>
@@ -3681,13 +3693,13 @@
         <v>115</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G8" s="26">
         <v>46365</v>
@@ -3714,10 +3726,10 @@
         <v>94</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P8" s="23" t="s">
         <v>97</v>
@@ -3725,7 +3737,9 @@
       <c r="Q8" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R8" s="23"/>
+      <c r="R8" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S8" s="30"/>
       <c r="T8" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3735,7 +3749,7 @@
         <v>23</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W8" s="30"/>
       <c r="X8" s="31"/>
@@ -3754,34 +3768,34 @@
       </c>
       <c r="AF8" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AG8" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH8" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D9" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>140</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>142</v>
       </c>
       <c r="G9" s="26">
         <v>46379</v>
@@ -3808,7 +3822,7 @@
         <v>94</v>
       </c>
       <c r="N9" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O9" s="23" t="s">
         <v>96</v>
@@ -3819,7 +3833,9 @@
       <c r="Q9" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R9" s="23"/>
+      <c r="R9" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S9" s="30"/>
       <c r="T9" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3829,7 +3845,7 @@
         <v>23</v>
       </c>
       <c r="V9" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W9" s="30"/>
       <c r="X9" s="31"/>
@@ -3848,19 +3864,19 @@
       </c>
       <c r="AF9" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AG9" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH9" s="28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:35" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>16</v>
@@ -3869,13 +3885,13 @@
         <v>115</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G10" s="26">
         <v>46463</v>
@@ -3902,10 +3918,10 @@
         <v>94</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P10" s="23" t="s">
         <v>97</v>
@@ -3913,7 +3929,9 @@
       <c r="Q10" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R10" s="23"/>
+      <c r="R10" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S10" s="30"/>
       <c r="T10" s="28" t="str">
         <f t="shared" si="3"/>
@@ -3923,7 +3941,7 @@
         <v>23</v>
       </c>
       <c r="V10" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W10" s="30"/>
       <c r="X10" s="31"/>
@@ -3942,19 +3960,19 @@
       </c>
       <c r="AF10" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG10" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH10" s="28" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>16</v>
@@ -3963,13 +3981,13 @@
         <v>107</v>
       </c>
       <c r="D11" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>151</v>
       </c>
       <c r="G11" s="26">
         <v>46477</v>
@@ -4007,7 +4025,9 @@
       <c r="Q11" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R11" s="23"/>
+      <c r="R11" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S11" s="30"/>
       <c r="T11" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4017,7 +4037,7 @@
         <v>23</v>
       </c>
       <c r="V11" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W11" s="30"/>
       <c r="X11" s="31"/>
@@ -4036,31 +4056,31 @@
       </c>
       <c r="AF11" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG11" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH11" s="28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="26">
@@ -4088,7 +4108,7 @@
         <v>94</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O12" s="23"/>
       <c r="P12" s="23" t="s">
@@ -4097,7 +4117,9 @@
       <c r="Q12" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R12" s="23"/>
+      <c r="R12" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S12" s="30"/>
       <c r="T12" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4107,7 +4129,7 @@
         <v>23</v>
       </c>
       <c r="V12" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W12" s="30"/>
       <c r="X12" s="31"/>
@@ -4126,31 +4148,31 @@
       </c>
       <c r="AF12" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG12" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH12" s="28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="26">
@@ -4178,7 +4200,7 @@
         <v>94</v>
       </c>
       <c r="N13" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O13" s="23"/>
       <c r="P13" s="23" t="s">
@@ -4187,7 +4209,9 @@
       <c r="Q13" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R13" s="23"/>
+      <c r="R13" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S13" s="30"/>
       <c r="T13" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4197,7 +4221,7 @@
         <v>23</v>
       </c>
       <c r="V13" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W13" s="30"/>
       <c r="X13" s="31"/>
@@ -4216,31 +4240,31 @@
       </c>
       <c r="AF13" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG13" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH13" s="28" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F14" s="23"/>
       <c r="G14" s="26">
@@ -4268,7 +4292,7 @@
         <v>94</v>
       </c>
       <c r="N14" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O14" s="23"/>
       <c r="P14" s="23" t="s">
@@ -4277,7 +4301,9 @@
       <c r="Q14" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="R14" s="23"/>
+      <c r="R14" s="23" t="s">
+        <v>231</v>
+      </c>
       <c r="S14" s="30"/>
       <c r="T14" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4287,7 +4313,7 @@
         <v>23</v>
       </c>
       <c r="V14" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W14" s="30"/>
       <c r="X14" s="31"/>
@@ -4306,34 +4332,34 @@
       </c>
       <c r="AF14" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG14" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
         <v/>
       </c>
       <c r="AH14" s="28" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="F15" s="23" t="s">
         <v>167</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>169</v>
       </c>
       <c r="G15" s="26">
         <v>46286</v>
@@ -4358,18 +4384,18 @@
       </c>
       <c r="M15" s="23"/>
       <c r="N15" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O15" s="23"/>
       <c r="P15" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q15" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R15" s="23"/>
       <c r="S15" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T15" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4382,11 +4408,15 @@
         <v>100</v>
       </c>
       <c r="W15" s="30"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="31"/>
-      <c r="Z15" s="32" t="str">
+      <c r="X15" s="31">
+        <v>102</v>
+      </c>
+      <c r="Y15" s="31">
+        <v>76</v>
+      </c>
+      <c r="Z15" s="32">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.74509803921568629</v>
       </c>
       <c r="AA15" s="33"/>
       <c r="AB15" s="34"/>
@@ -4408,22 +4438,22 @@
     </row>
     <row r="16" spans="1:35" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G16" s="26">
         <v>46300</v>
@@ -4448,28 +4478,28 @@
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O16" s="23"/>
       <c r="P16" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q16" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R16" s="23"/>
       <c r="S16" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T16" s="28" t="str">
         <f t="shared" si="3"/>
         <v>Published</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V16" s="30" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="W16" s="30"/>
       <c r="X16" s="31"/>
@@ -4484,36 +4514,36 @@
       <c r="AD16" s="34"/>
       <c r="AE16" s="28" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Next 14 days</v>
+        <v>In progress</v>
       </c>
       <c r="AF16" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>Announce</v>
+        <v/>
       </c>
       <c r="AH16" s="28"/>
     </row>
     <row r="17" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G17" s="26">
         <v>46314</v>
@@ -4538,18 +4568,18 @@
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q17" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R17" s="23"/>
       <c r="S17" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T17" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4559,7 +4589,7 @@
         <v>25</v>
       </c>
       <c r="V17" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W17" s="30"/>
       <c r="X17" s="31"/>
@@ -4574,36 +4604,36 @@
       <c r="AD17" s="34"/>
       <c r="AE17" s="28" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Next 45 days</v>
+        <v>Next 14 days</v>
       </c>
       <c r="AF17" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG17" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v/>
+        <v>Announce</v>
       </c>
       <c r="AH17" s="28"/>
     </row>
     <row r="18" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G18" s="26">
         <v>46335</v>
@@ -4628,18 +4658,18 @@
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O18" s="23"/>
       <c r="P18" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q18" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R18" s="23"/>
       <c r="S18" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T18" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4649,7 +4679,7 @@
         <v>25</v>
       </c>
       <c r="V18" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W18" s="30"/>
       <c r="X18" s="31"/>
@@ -4668,7 +4698,7 @@
       </c>
       <c r="AF18" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG18" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4678,22 +4708,22 @@
     </row>
     <row r="19" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G19" s="26">
         <v>46349</v>
@@ -4718,18 +4748,18 @@
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O19" s="23"/>
       <c r="P19" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q19" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R19" s="23"/>
       <c r="S19" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T19" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4739,7 +4769,7 @@
         <v>25</v>
       </c>
       <c r="V19" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W19" s="30"/>
       <c r="X19" s="31"/>
@@ -4758,7 +4788,7 @@
       </c>
       <c r="AF19" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AG19" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4768,22 +4798,22 @@
     </row>
     <row r="20" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G20" s="26">
         <v>46363</v>
@@ -4808,18 +4838,18 @@
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O20" s="23"/>
       <c r="P20" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q20" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R20" s="23"/>
       <c r="S20" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T20" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4829,7 +4859,7 @@
         <v>25</v>
       </c>
       <c r="V20" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W20" s="30"/>
       <c r="X20" s="31"/>
@@ -4848,7 +4878,7 @@
       </c>
       <c r="AF20" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG20" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4858,22 +4888,22 @@
     </row>
     <row r="21" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G21" s="26">
         <v>46377</v>
@@ -4898,18 +4928,18 @@
       </c>
       <c r="M21" s="23"/>
       <c r="N21" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O21" s="23"/>
       <c r="P21" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q21" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R21" s="23"/>
       <c r="S21" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T21" s="28" t="str">
         <f t="shared" si="3"/>
@@ -4919,7 +4949,7 @@
         <v>25</v>
       </c>
       <c r="V21" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W21" s="30"/>
       <c r="X21" s="31"/>
@@ -4938,7 +4968,7 @@
       </c>
       <c r="AF21" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG21" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -4948,22 +4978,22 @@
     </row>
     <row r="22" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G22" s="26">
         <v>46391</v>
@@ -4988,18 +5018,18 @@
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O22" s="23"/>
       <c r="P22" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q22" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R22" s="23"/>
       <c r="S22" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T22" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5009,7 +5039,7 @@
         <v>25</v>
       </c>
       <c r="V22" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W22" s="30"/>
       <c r="X22" s="31"/>
@@ -5028,7 +5058,7 @@
       </c>
       <c r="AF22" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG22" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5038,22 +5068,22 @@
     </row>
     <row r="23" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G23" s="26">
         <v>46405</v>
@@ -5078,18 +5108,18 @@
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O23" s="23"/>
       <c r="P23" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q23" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R23" s="23"/>
       <c r="S23" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T23" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5099,7 +5129,7 @@
         <v>25</v>
       </c>
       <c r="V23" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W23" s="30"/>
       <c r="X23" s="31"/>
@@ -5118,7 +5148,7 @@
       </c>
       <c r="AF23" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG23" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5128,22 +5158,22 @@
     </row>
     <row r="24" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G24" s="26">
         <v>46426</v>
@@ -5168,18 +5198,18 @@
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O24" s="23"/>
       <c r="P24" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q24" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R24" s="23"/>
       <c r="S24" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T24" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5189,7 +5219,7 @@
         <v>25</v>
       </c>
       <c r="V24" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W24" s="30"/>
       <c r="X24" s="31"/>
@@ -5208,7 +5238,7 @@
       </c>
       <c r="AF24" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG24" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5218,22 +5248,22 @@
     </row>
     <row r="25" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G25" s="26">
         <v>46440</v>
@@ -5258,18 +5288,18 @@
       </c>
       <c r="M25" s="23"/>
       <c r="N25" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O25" s="23"/>
       <c r="P25" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q25" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R25" s="23"/>
       <c r="S25" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T25" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5279,7 +5309,7 @@
         <v>25</v>
       </c>
       <c r="V25" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W25" s="30"/>
       <c r="X25" s="31"/>
@@ -5298,7 +5328,7 @@
       </c>
       <c r="AF25" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG25" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5308,22 +5338,22 @@
     </row>
     <row r="26" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G26" s="26">
         <v>46454</v>
@@ -5348,18 +5378,18 @@
       </c>
       <c r="M26" s="23"/>
       <c r="N26" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O26" s="23"/>
       <c r="P26" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q26" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R26" s="23"/>
       <c r="S26" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T26" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5369,7 +5399,7 @@
         <v>25</v>
       </c>
       <c r="V26" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W26" s="30"/>
       <c r="X26" s="31"/>
@@ -5388,7 +5418,7 @@
       </c>
       <c r="AF26" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG26" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5398,22 +5428,22 @@
     </row>
     <row r="27" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G27" s="26">
         <v>46468</v>
@@ -5438,18 +5468,18 @@
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O27" s="23"/>
       <c r="P27" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q27" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R27" s="23"/>
       <c r="S27" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T27" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5459,7 +5489,7 @@
         <v>25</v>
       </c>
       <c r="V27" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W27" s="30"/>
       <c r="X27" s="31"/>
@@ -5478,7 +5508,7 @@
       </c>
       <c r="AF27" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG27" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5488,22 +5518,22 @@
     </row>
     <row r="28" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G28" s="26">
         <v>46482</v>
@@ -5528,18 +5558,18 @@
       </c>
       <c r="M28" s="23"/>
       <c r="N28" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O28" s="23"/>
       <c r="P28" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q28" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R28" s="23"/>
       <c r="S28" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T28" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5549,7 +5579,7 @@
         <v>25</v>
       </c>
       <c r="V28" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W28" s="30"/>
       <c r="X28" s="31"/>
@@ -5568,7 +5598,7 @@
       </c>
       <c r="AF28" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG28" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5578,22 +5608,22 @@
     </row>
     <row r="29" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G29" s="26">
         <v>46496</v>
@@ -5618,18 +5648,18 @@
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O29" s="23"/>
       <c r="P29" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q29" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R29" s="23"/>
       <c r="S29" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T29" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5639,7 +5669,7 @@
         <v>25</v>
       </c>
       <c r="V29" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W29" s="30"/>
       <c r="X29" s="31"/>
@@ -5658,7 +5688,7 @@
       </c>
       <c r="AF29" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG29" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5668,22 +5698,22 @@
     </row>
     <row r="30" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G30" s="26">
         <v>46510</v>
@@ -5708,18 +5738,18 @@
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O30" s="23"/>
       <c r="P30" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q30" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R30" s="23"/>
       <c r="S30" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T30" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5729,7 +5759,7 @@
         <v>25</v>
       </c>
       <c r="V30" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W30" s="30"/>
       <c r="X30" s="31"/>
@@ -5748,7 +5778,7 @@
       </c>
       <c r="AF30" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AG30" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5758,22 +5788,22 @@
     </row>
     <row r="31" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G31" s="26">
         <v>46531</v>
@@ -5798,18 +5828,18 @@
       </c>
       <c r="M31" s="23"/>
       <c r="N31" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q31" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R31" s="23"/>
       <c r="S31" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T31" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5819,7 +5849,7 @@
         <v>25</v>
       </c>
       <c r="V31" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W31" s="30"/>
       <c r="X31" s="31"/>
@@ -5838,7 +5868,7 @@
       </c>
       <c r="AF31" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG31" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5848,22 +5878,22 @@
     </row>
     <row r="32" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G32" s="26">
         <v>46545</v>
@@ -5888,18 +5918,18 @@
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O32" s="23"/>
       <c r="P32" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q32" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R32" s="23"/>
       <c r="S32" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T32" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5909,7 +5939,7 @@
         <v>25</v>
       </c>
       <c r="V32" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W32" s="30"/>
       <c r="X32" s="31"/>
@@ -5928,7 +5958,7 @@
       </c>
       <c r="AF32" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG32" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -5938,22 +5968,22 @@
     </row>
     <row r="33" spans="1:34" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G33" s="26">
         <v>46559</v>
@@ -5978,18 +6008,18 @@
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O33" s="23"/>
       <c r="P33" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q33" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R33" s="23"/>
       <c r="S33" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="T33" s="28" t="str">
         <f t="shared" si="3"/>
@@ -5999,7 +6029,7 @@
         <v>25</v>
       </c>
       <c r="V33" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W33" s="30"/>
       <c r="X33" s="31"/>
@@ -6018,7 +6048,7 @@
       </c>
       <c r="AF33" s="28">
         <f t="shared" ca="1" si="6"/>
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG33" s="28" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -6028,19 +6058,19 @@
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="E34" s="25" t="s">
         <v>228</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>230</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>18</v>
@@ -6068,20 +6098,20 @@
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O34" s="23"/>
       <c r="P34" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q34" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S34" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="T34" s="28" t="str">
         <f t="shared" ref="T34:T65" si="11">IF(TRIM(S34)="","Missing","Published")</f>
@@ -6120,24 +6150,24 @@
         <v>33</v>
       </c>
       <c r="AH34" s="28" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>18</v>
@@ -6165,20 +6195,20 @@
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O35" s="23"/>
       <c r="P35" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q35" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="T35" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6207,35 +6237,35 @@
       <c r="AD35" s="34"/>
       <c r="AE35" s="28" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Next 14 days</v>
+        <v>In progress</v>
       </c>
       <c r="AF35" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="28" t="str">
         <f t="shared" ref="AG35:AG65" ca="1" si="15">IF(AND(AE35="Past",U35&lt;&gt;"Delivered",U35&lt;&gt;"Cancelled",U35&lt;&gt;"Postponed"),"Update status",IF(AND(T35="Missing",OR(AE35="In progress",AE35="Next 14 days")),"Add link",IF(AND(AE35="Next 14 days",V35&lt;&gt;"Published"),"Announce","")))</f>
         <v/>
       </c>
       <c r="AH35" s="28" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>18</v>
@@ -6263,20 +6293,20 @@
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O36" s="23"/>
       <c r="P36" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q36" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="T36" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6305,28 +6335,28 @@
       </c>
       <c r="AF36" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG36" s="28"/>
       <c r="AH36" s="28" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E37" s="25" t="s">
         <v>249</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>251</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>18</v>
@@ -6354,20 +6384,20 @@
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O37" s="23"/>
       <c r="P37" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q37" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R37" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S37" s="29" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T37" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6377,7 +6407,7 @@
         <v>25</v>
       </c>
       <c r="V37" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W37" s="30"/>
       <c r="X37" s="31"/>
@@ -6396,31 +6426,31 @@
       </c>
       <c r="AF37" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG37" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v>Announce</v>
       </c>
       <c r="AH37" s="28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A38" s="23" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>18</v>
@@ -6448,17 +6478,17 @@
       </c>
       <c r="M38" s="23"/>
       <c r="N38" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O38" s="23"/>
       <c r="P38" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q38" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S38" s="30"/>
       <c r="T38" s="28" t="str">
@@ -6469,7 +6499,7 @@
         <v>23</v>
       </c>
       <c r="V38" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W38" s="30"/>
       <c r="X38" s="31"/>
@@ -6484,35 +6514,35 @@
       <c r="AD38" s="34"/>
       <c r="AE38" s="28" t="str">
         <f t="shared" ca="1" si="13"/>
-        <v>Next 45 days</v>
+        <v>Next 14 days</v>
       </c>
       <c r="AF38" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG38" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
-        <v/>
+        <v>Add link</v>
       </c>
       <c r="AH38" s="28" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>18</v>
@@ -6540,20 +6570,20 @@
       </c>
       <c r="M39" s="23"/>
       <c r="N39" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O39" s="23"/>
       <c r="P39" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q39" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="T39" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6563,7 +6593,7 @@
         <v>25</v>
       </c>
       <c r="V39" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W39" s="30"/>
       <c r="X39" s="31"/>
@@ -6582,31 +6612,31 @@
       </c>
       <c r="AF39" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG39" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH39" s="28" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>18</v>
@@ -6634,20 +6664,20 @@
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O40" s="23"/>
       <c r="P40" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q40" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="T40" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6657,7 +6687,7 @@
         <v>25</v>
       </c>
       <c r="V40" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W40" s="30"/>
       <c r="X40" s="31"/>
@@ -6676,31 +6706,31 @@
       </c>
       <c r="AF40" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG40" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH40" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>18</v>
@@ -6728,20 +6758,20 @@
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="O41" s="23"/>
       <c r="P41" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q41" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R41" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S41" s="29" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="T41" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6751,7 +6781,7 @@
         <v>25</v>
       </c>
       <c r="V41" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W41" s="30"/>
       <c r="X41" s="31"/>
@@ -6770,31 +6800,31 @@
       </c>
       <c r="AF41" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG41" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH41" s="28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F42" s="23" t="s">
         <v>18</v>
@@ -6822,17 +6852,17 @@
       </c>
       <c r="M42" s="23"/>
       <c r="N42" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O42" s="23"/>
       <c r="P42" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q42" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S42" s="30"/>
       <c r="T42" s="28" t="str">
@@ -6843,7 +6873,7 @@
         <v>23</v>
       </c>
       <c r="V42" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W42" s="30"/>
       <c r="X42" s="31"/>
@@ -6862,31 +6892,31 @@
       </c>
       <c r="AF42" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG42" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH42" s="28" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>18</v>
@@ -6914,20 +6944,20 @@
       </c>
       <c r="M43" s="23"/>
       <c r="N43" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O43" s="23"/>
       <c r="P43" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q43" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S43" s="29" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="T43" s="28" t="str">
         <f t="shared" si="11"/>
@@ -6937,7 +6967,7 @@
         <v>25</v>
       </c>
       <c r="V43" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W43" s="30"/>
       <c r="X43" s="31"/>
@@ -6956,31 +6986,31 @@
       </c>
       <c r="AF43" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AG43" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH43" s="28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A44" s="23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>18</v>
@@ -7008,20 +7038,20 @@
       </c>
       <c r="M44" s="23"/>
       <c r="N44" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O44" s="23"/>
       <c r="P44" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q44" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R44" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S44" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T44" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7031,7 +7061,7 @@
         <v>25</v>
       </c>
       <c r="V44" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W44" s="30"/>
       <c r="X44" s="31"/>
@@ -7050,31 +7080,31 @@
       </c>
       <c r="AF44" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AG44" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH44" s="28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A45" s="23" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B45" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>18</v>
@@ -7102,20 +7132,20 @@
       </c>
       <c r="M45" s="23"/>
       <c r="N45" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O45" s="23"/>
       <c r="P45" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q45" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R45" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S45" s="29" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T45" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7125,7 +7155,7 @@
         <v>25</v>
       </c>
       <c r="V45" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W45" s="30"/>
       <c r="X45" s="31"/>
@@ -7144,31 +7174,31 @@
       </c>
       <c r="AF45" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG45" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH45" s="28" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A46" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>18</v>
@@ -7196,20 +7226,20 @@
       </c>
       <c r="M46" s="23"/>
       <c r="N46" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O46" s="23"/>
       <c r="P46" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q46" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R46" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S46" s="29" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="T46" s="28" t="str">
         <f t="shared" si="11"/>
@@ -7219,7 +7249,7 @@
         <v>25</v>
       </c>
       <c r="V46" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W46" s="30"/>
       <c r="X46" s="31"/>
@@ -7238,31 +7268,31 @@
       </c>
       <c r="AF46" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AG46" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH46" s="28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>18</v>
@@ -7290,17 +7320,17 @@
       </c>
       <c r="M47" s="23"/>
       <c r="N47" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O47" s="23"/>
       <c r="P47" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q47" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R47" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S47" s="30"/>
       <c r="T47" s="28" t="str">
@@ -7311,7 +7341,7 @@
         <v>23</v>
       </c>
       <c r="V47" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W47" s="30"/>
       <c r="X47" s="31"/>
@@ -7330,31 +7360,31 @@
       </c>
       <c r="AF47" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG47" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH47" s="28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A48" s="23" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>18</v>
@@ -7382,17 +7412,17 @@
       </c>
       <c r="M48" s="23"/>
       <c r="N48" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O48" s="23"/>
       <c r="P48" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q48" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R48" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S48" s="30"/>
       <c r="T48" s="28" t="str">
@@ -7403,7 +7433,7 @@
         <v>23</v>
       </c>
       <c r="V48" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W48" s="30"/>
       <c r="X48" s="31"/>
@@ -7422,31 +7452,31 @@
       </c>
       <c r="AF48" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG48" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH48" s="28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A49" s="23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C49" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E49" s="25" t="s">
         <v>312</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>314</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>18</v>
@@ -7474,17 +7504,17 @@
       </c>
       <c r="M49" s="23"/>
       <c r="N49" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O49" s="23"/>
       <c r="P49" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q49" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S49" s="30"/>
       <c r="T49" s="28" t="str">
@@ -7495,7 +7525,7 @@
         <v>23</v>
       </c>
       <c r="V49" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W49" s="30"/>
       <c r="X49" s="31"/>
@@ -7514,31 +7544,31 @@
       </c>
       <c r="AF49" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG49" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH49" s="28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>18</v>
@@ -7566,17 +7596,17 @@
       </c>
       <c r="M50" s="23"/>
       <c r="N50" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O50" s="23"/>
       <c r="P50" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q50" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S50" s="30"/>
       <c r="T50" s="28" t="str">
@@ -7587,7 +7617,7 @@
         <v>23</v>
       </c>
       <c r="V50" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W50" s="30"/>
       <c r="X50" s="31"/>
@@ -7606,31 +7636,31 @@
       </c>
       <c r="AF50" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG50" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH50" s="28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>18</v>
@@ -7658,17 +7688,17 @@
       </c>
       <c r="M51" s="23"/>
       <c r="N51" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O51" s="23"/>
       <c r="P51" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q51" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R51" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S51" s="30"/>
       <c r="T51" s="28" t="str">
@@ -7679,7 +7709,7 @@
         <v>23</v>
       </c>
       <c r="V51" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W51" s="30"/>
       <c r="X51" s="31"/>
@@ -7698,31 +7728,31 @@
       </c>
       <c r="AF51" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG51" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH51" s="28" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A52" s="23" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>18</v>
@@ -7750,17 +7780,17 @@
       </c>
       <c r="M52" s="23"/>
       <c r="N52" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O52" s="23"/>
       <c r="P52" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q52" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R52" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S52" s="30"/>
       <c r="T52" s="28" t="str">
@@ -7771,7 +7801,7 @@
         <v>23</v>
       </c>
       <c r="V52" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W52" s="30"/>
       <c r="X52" s="31"/>
@@ -7790,31 +7820,31 @@
       </c>
       <c r="AF52" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG52" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH52" s="28" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A53" s="23" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B53" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F53" s="23" t="s">
         <v>18</v>
@@ -7842,17 +7872,17 @@
       </c>
       <c r="M53" s="23"/>
       <c r="N53" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O53" s="23"/>
       <c r="P53" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q53" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R53" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S53" s="30"/>
       <c r="T53" s="28" t="str">
@@ -7863,7 +7893,7 @@
         <v>23</v>
       </c>
       <c r="V53" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W53" s="30"/>
       <c r="X53" s="31"/>
@@ -7882,31 +7912,31 @@
       </c>
       <c r="AF53" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG53" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH53" s="28" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F54" s="23" t="s">
         <v>18</v>
@@ -7934,17 +7964,17 @@
       </c>
       <c r="M54" s="23"/>
       <c r="N54" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O54" s="23"/>
       <c r="P54" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q54" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R54" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S54" s="30"/>
       <c r="T54" s="28" t="str">
@@ -7955,7 +7985,7 @@
         <v>23</v>
       </c>
       <c r="V54" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W54" s="30"/>
       <c r="X54" s="31"/>
@@ -7974,31 +8004,31 @@
       </c>
       <c r="AF54" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG54" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH54" s="28" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B55" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F55" s="23" t="s">
         <v>18</v>
@@ -8026,17 +8056,17 @@
       </c>
       <c r="M55" s="23"/>
       <c r="N55" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O55" s="23"/>
       <c r="P55" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q55" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R55" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S55" s="30"/>
       <c r="T55" s="28" t="str">
@@ -8047,7 +8077,7 @@
         <v>23</v>
       </c>
       <c r="V55" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W55" s="30"/>
       <c r="X55" s="31"/>
@@ -8066,31 +8096,31 @@
       </c>
       <c r="AF55" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG55" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH55" s="28" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A56" s="23" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B56" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>18</v>
@@ -8118,17 +8148,17 @@
       </c>
       <c r="M56" s="23"/>
       <c r="N56" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="O56" s="23"/>
       <c r="P56" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q56" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R56" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S56" s="30"/>
       <c r="T56" s="28" t="str">
@@ -8139,7 +8169,7 @@
         <v>23</v>
       </c>
       <c r="V56" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W56" s="30"/>
       <c r="X56" s="31"/>
@@ -8158,31 +8188,31 @@
       </c>
       <c r="AF56" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG56" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH56" s="28" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F57" s="23" t="s">
         <v>18</v>
@@ -8210,17 +8240,17 @@
       </c>
       <c r="M57" s="23"/>
       <c r="N57" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O57" s="23"/>
       <c r="P57" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q57" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S57" s="30"/>
       <c r="T57" s="28" t="str">
@@ -8231,7 +8261,7 @@
         <v>23</v>
       </c>
       <c r="V57" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W57" s="30"/>
       <c r="X57" s="31"/>
@@ -8250,31 +8280,31 @@
       </c>
       <c r="AF57" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG57" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH57" s="28" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F58" s="23" t="s">
         <v>18</v>
@@ -8302,17 +8332,17 @@
       </c>
       <c r="M58" s="23"/>
       <c r="N58" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O58" s="23"/>
       <c r="P58" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q58" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R58" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S58" s="30"/>
       <c r="T58" s="28" t="str">
@@ -8323,7 +8353,7 @@
         <v>23</v>
       </c>
       <c r="V58" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W58" s="30"/>
       <c r="X58" s="31"/>
@@ -8342,31 +8372,31 @@
       </c>
       <c r="AF58" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG58" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH58" s="28" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B59" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F59" s="23" t="s">
         <v>18</v>
@@ -8394,17 +8424,17 @@
       </c>
       <c r="M59" s="23"/>
       <c r="N59" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O59" s="23"/>
       <c r="P59" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q59" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R59" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S59" s="30"/>
       <c r="T59" s="28" t="str">
@@ -8415,7 +8445,7 @@
         <v>23</v>
       </c>
       <c r="V59" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W59" s="30"/>
       <c r="X59" s="31"/>
@@ -8434,31 +8464,31 @@
       </c>
       <c r="AF59" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG59" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH59" s="28" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A60" s="23" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F60" s="23" t="s">
         <v>18</v>
@@ -8486,17 +8516,17 @@
       </c>
       <c r="M60" s="23"/>
       <c r="N60" s="24" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O60" s="23"/>
       <c r="P60" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q60" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R60" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S60" s="30"/>
       <c r="T60" s="28" t="str">
@@ -8507,7 +8537,7 @@
         <v>23</v>
       </c>
       <c r="V60" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W60" s="30"/>
       <c r="X60" s="31"/>
@@ -8526,31 +8556,31 @@
       </c>
       <c r="AF60" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG60" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH60" s="28" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A61" s="23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B61" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F61" s="23" t="s">
         <v>18</v>
@@ -8578,17 +8608,17 @@
       </c>
       <c r="M61" s="23"/>
       <c r="N61" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O61" s="23"/>
       <c r="P61" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q61" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S61" s="30"/>
       <c r="T61" s="28" t="str">
@@ -8599,7 +8629,7 @@
         <v>23</v>
       </c>
       <c r="V61" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W61" s="30"/>
       <c r="X61" s="31"/>
@@ -8618,31 +8648,31 @@
       </c>
       <c r="AF61" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG61" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH61" s="28" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B62" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F62" s="23" t="s">
         <v>18</v>
@@ -8670,17 +8700,17 @@
       </c>
       <c r="M62" s="23"/>
       <c r="N62" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O62" s="23"/>
       <c r="P62" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q62" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S62" s="30"/>
       <c r="T62" s="28" t="str">
@@ -8691,7 +8721,7 @@
         <v>23</v>
       </c>
       <c r="V62" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W62" s="30"/>
       <c r="X62" s="31"/>
@@ -8710,31 +8740,31 @@
       </c>
       <c r="AF62" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG62" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH62" s="28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A63" s="23" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B63" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F63" s="23" t="s">
         <v>18</v>
@@ -8762,17 +8792,17 @@
       </c>
       <c r="M63" s="23"/>
       <c r="N63" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O63" s="23"/>
       <c r="P63" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q63" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R63" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S63" s="30"/>
       <c r="T63" s="28" t="str">
@@ -8783,7 +8813,7 @@
         <v>23</v>
       </c>
       <c r="V63" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W63" s="30"/>
       <c r="X63" s="31"/>
@@ -8802,31 +8832,31 @@
       </c>
       <c r="AF63" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG63" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH63" s="28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A64" s="23" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F64" s="23" t="s">
         <v>18</v>
@@ -8854,17 +8884,17 @@
       </c>
       <c r="M64" s="23"/>
       <c r="N64" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O64" s="23"/>
       <c r="P64" s="23" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="Q64" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R64" s="23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S64" s="30"/>
       <c r="T64" s="28" t="str">
@@ -8875,7 +8905,7 @@
         <v>23</v>
       </c>
       <c r="V64" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W64" s="30"/>
       <c r="X64" s="31"/>
@@ -8894,31 +8924,31 @@
       </c>
       <c r="AF64" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG64" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH64" s="28" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A65" s="23" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>18</v>
@@ -8946,17 +8976,17 @@
       </c>
       <c r="M65" s="23"/>
       <c r="N65" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="O65" s="23"/>
       <c r="P65" s="23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="23" t="s">
         <v>98</v>
       </c>
       <c r="R65" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="S65" s="30"/>
       <c r="T65" s="28" t="str">
@@ -8967,7 +8997,7 @@
         <v>23</v>
       </c>
       <c r="V65" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W65" s="30"/>
       <c r="X65" s="31"/>
@@ -8986,34 +9016,34 @@
       </c>
       <c r="AF65" s="28">
         <f t="shared" ca="1" si="14"/>
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AG65" s="28" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
       <c r="AH65" s="28" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C66" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="E66" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="F66" s="23" t="s">
         <v>384</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>386</v>
       </c>
       <c r="G66" s="26">
         <v>46321</v>
@@ -9038,7 +9068,7 @@
       </c>
       <c r="M66" s="23"/>
       <c r="N66" s="24" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O66" s="23"/>
       <c r="P66" s="23"/>
@@ -9055,7 +9085,7 @@
         <v>23</v>
       </c>
       <c r="V66" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W66" s="30"/>
       <c r="X66" s="31"/>
@@ -9074,34 +9104,34 @@
       </c>
       <c r="AF66" s="28">
         <f t="shared" ref="AF66:AF81" ca="1" si="22">IF(G66="","",IF(H66&lt;TODAY(),"",G66-TODAY()))</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG66" s="28" t="str">
         <f t="shared" ref="AG66:AG81" ca="1" si="23">IF(AND(AE66="Past",U66&lt;&gt;"Delivered",U66&lt;&gt;"Cancelled",U66&lt;&gt;"Postponed"),"Update status",IF(AND(T66="Missing",OR(AE66="In progress",AE66="Next 14 days")),"Add link",IF(AND(AE66="Next 14 days",V66&lt;&gt;"Published"),"Announce","")))</f>
         <v/>
       </c>
       <c r="AH66" s="28" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A67" s="23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B67" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C67" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="E67" s="25" t="s">
         <v>390</v>
       </c>
-      <c r="D67" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>392</v>
-      </c>
       <c r="F67" s="23" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G67" s="26">
         <v>46419</v>
@@ -9126,7 +9156,7 @@
       </c>
       <c r="M67" s="23"/>
       <c r="N67" s="24" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O67" s="23"/>
       <c r="P67" s="23"/>
@@ -9143,7 +9173,7 @@
         <v>23</v>
       </c>
       <c r="V67" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W67" s="30"/>
       <c r="X67" s="31"/>
@@ -9162,34 +9192,34 @@
       </c>
       <c r="AF67" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG67" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH67" s="28" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A68" s="23" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="E68" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="D68" s="24" t="s">
+      <c r="F68" s="23" t="s">
         <v>396</v>
-      </c>
-      <c r="E68" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>398</v>
       </c>
       <c r="G68" s="26">
         <v>46419</v>
@@ -9198,7 +9228,7 @@
         <v>46446</v>
       </c>
       <c r="I68" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J68" s="27">
         <f t="shared" si="16"/>
@@ -9214,7 +9244,7 @@
       </c>
       <c r="M68" s="23"/>
       <c r="N68" s="24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O68" s="23"/>
       <c r="P68" s="23"/>
@@ -9231,7 +9261,7 @@
         <v>23</v>
       </c>
       <c r="V68" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W68" s="30"/>
       <c r="X68" s="31"/>
@@ -9250,34 +9280,34 @@
       </c>
       <c r="AF68" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG68" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH68" s="28" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="69" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A69" s="23" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>19</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G69" s="26">
         <v>46497</v>
@@ -9302,7 +9332,7 @@
       </c>
       <c r="M69" s="23"/>
       <c r="N69" s="24" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O69" s="23"/>
       <c r="P69" s="23"/>
@@ -9319,7 +9349,7 @@
         <v>23</v>
       </c>
       <c r="V69" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W69" s="30"/>
       <c r="X69" s="31"/>
@@ -9338,34 +9368,34 @@
       </c>
       <c r="AF69" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG69" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH69" s="28" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="70" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A70" s="23" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C70" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E70" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="F70" s="23" t="s">
         <v>408</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>410</v>
       </c>
       <c r="G70" s="26">
         <v>46357</v>
@@ -9374,7 +9404,7 @@
         <v>46387</v>
       </c>
       <c r="I70" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J70" s="27">
         <f t="shared" si="16"/>
@@ -9392,10 +9422,10 @@
       <c r="N70" s="24"/>
       <c r="O70" s="23"/>
       <c r="P70" s="23" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="Q70" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R70" s="23"/>
       <c r="S70" s="30"/>
@@ -9407,7 +9437,7 @@
         <v>23</v>
       </c>
       <c r="V70" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W70" s="30"/>
       <c r="X70" s="31"/>
@@ -9426,34 +9456,34 @@
       </c>
       <c r="AF70" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG70" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH70" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="71" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A71" s="23" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E71" s="25" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G71" s="26">
         <v>46357</v>
@@ -9462,7 +9492,7 @@
         <v>46387</v>
       </c>
       <c r="I71" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J71" s="27">
         <f t="shared" si="16"/>
@@ -9480,10 +9510,10 @@
       <c r="N71" s="24"/>
       <c r="O71" s="23"/>
       <c r="P71" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R71" s="23"/>
       <c r="S71" s="30"/>
@@ -9495,7 +9525,7 @@
         <v>23</v>
       </c>
       <c r="V71" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W71" s="30"/>
       <c r="X71" s="31"/>
@@ -9514,34 +9544,34 @@
       </c>
       <c r="AF71" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AG71" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH71" s="28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="72" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A72" s="23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C72" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E72" s="25" t="s">
         <v>419</v>
       </c>
-      <c r="D72" s="24" t="s">
+      <c r="F72" s="23" t="s">
         <v>420</v>
-      </c>
-      <c r="E72" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>422</v>
       </c>
       <c r="G72" s="26">
         <v>46388</v>
@@ -9550,7 +9580,7 @@
         <v>46418</v>
       </c>
       <c r="I72" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J72" s="27">
         <f t="shared" si="16"/>
@@ -9568,10 +9598,10 @@
       <c r="N72" s="24"/>
       <c r="O72" s="23"/>
       <c r="P72" s="23" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q72" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R72" s="23"/>
       <c r="S72" s="30"/>
@@ -9583,7 +9613,7 @@
         <v>23</v>
       </c>
       <c r="V72" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W72" s="30"/>
       <c r="X72" s="31"/>
@@ -9602,34 +9632,34 @@
       </c>
       <c r="AF72" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AG72" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH72" s="28" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A73" s="23" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="E73" s="25" t="s">
         <v>426</v>
       </c>
-      <c r="D73" s="24" t="s">
-        <v>427</v>
-      </c>
-      <c r="E73" s="25" t="s">
-        <v>428</v>
-      </c>
       <c r="F73" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G73" s="26">
         <v>46419</v>
@@ -9638,7 +9668,7 @@
         <v>46446</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J73" s="27">
         <f t="shared" si="16"/>
@@ -9656,10 +9686,10 @@
       <c r="N73" s="24"/>
       <c r="O73" s="23"/>
       <c r="P73" s="23" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q73" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R73" s="23"/>
       <c r="S73" s="30"/>
@@ -9671,7 +9701,7 @@
         <v>23</v>
       </c>
       <c r="V73" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W73" s="30"/>
       <c r="X73" s="31"/>
@@ -9690,34 +9720,34 @@
       </c>
       <c r="AF73" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG73" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH73" s="28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A74" s="23" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C74" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="E74" s="25" t="s">
         <v>432</v>
       </c>
-      <c r="D74" s="24" t="s">
-        <v>433</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>434</v>
-      </c>
       <c r="F74" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G74" s="26">
         <v>46447</v>
@@ -9726,7 +9756,7 @@
         <v>46477</v>
       </c>
       <c r="I74" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J74" s="27">
         <f t="shared" si="16"/>
@@ -9744,10 +9774,10 @@
       <c r="N74" s="24"/>
       <c r="O74" s="23"/>
       <c r="P74" s="23" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q74" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R74" s="23"/>
       <c r="S74" s="30"/>
@@ -9759,7 +9789,7 @@
         <v>23</v>
       </c>
       <c r="V74" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W74" s="30"/>
       <c r="X74" s="31"/>
@@ -9778,34 +9808,34 @@
       </c>
       <c r="AF74" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG74" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH74" s="28" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A75" s="23" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E75" s="25" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G75" s="26">
         <v>46447</v>
@@ -9814,7 +9844,7 @@
         <v>46477</v>
       </c>
       <c r="I75" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J75" s="27">
         <f t="shared" si="16"/>
@@ -9832,10 +9862,10 @@
       <c r="N75" s="24"/>
       <c r="O75" s="23"/>
       <c r="P75" s="23" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Q75" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R75" s="23"/>
       <c r="S75" s="30"/>
@@ -9847,7 +9877,7 @@
         <v>23</v>
       </c>
       <c r="V75" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W75" s="30"/>
       <c r="X75" s="31"/>
@@ -9866,34 +9896,34 @@
       </c>
       <c r="AF75" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG75" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH75" s="28" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A76" s="23" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B76" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E76" s="25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G76" s="26">
         <v>46478</v>
@@ -9902,7 +9932,7 @@
         <v>46507</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J76" s="27">
         <f t="shared" si="16"/>
@@ -9920,10 +9950,10 @@
       <c r="N76" s="24"/>
       <c r="O76" s="23"/>
       <c r="P76" s="23" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q76" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R76" s="23"/>
       <c r="S76" s="30"/>
@@ -9935,7 +9965,7 @@
         <v>23</v>
       </c>
       <c r="V76" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W76" s="30"/>
       <c r="X76" s="31"/>
@@ -9954,34 +9984,34 @@
       </c>
       <c r="AF76" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG76" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH76" s="28" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="77" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A77" s="23" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B77" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E77" s="25" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G77" s="26">
         <v>46478</v>
@@ -9990,7 +10020,7 @@
         <v>46507</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J77" s="27">
         <f t="shared" si="16"/>
@@ -10008,10 +10038,10 @@
       <c r="N77" s="24"/>
       <c r="O77" s="23"/>
       <c r="P77" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q77" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R77" s="23"/>
       <c r="S77" s="30"/>
@@ -10023,7 +10053,7 @@
         <v>23</v>
       </c>
       <c r="V77" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W77" s="30"/>
       <c r="X77" s="31"/>
@@ -10042,34 +10072,34 @@
       </c>
       <c r="AF77" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG77" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH77" s="28" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="78" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A78" s="23" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E78" s="25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G78" s="26">
         <v>46478</v>
@@ -10078,7 +10108,7 @@
         <v>46507</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J78" s="27">
         <f t="shared" si="16"/>
@@ -10096,10 +10126,10 @@
       <c r="N78" s="24"/>
       <c r="O78" s="23"/>
       <c r="P78" s="23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q78" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R78" s="23"/>
       <c r="S78" s="30"/>
@@ -10111,7 +10141,7 @@
         <v>23</v>
       </c>
       <c r="V78" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W78" s="30"/>
       <c r="X78" s="31"/>
@@ -10130,34 +10160,34 @@
       </c>
       <c r="AF78" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG78" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH78" s="28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A79" s="23" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G79" s="26">
         <v>46489</v>
@@ -10185,7 +10215,7 @@
       <c r="O79" s="23"/>
       <c r="P79" s="23"/>
       <c r="Q79" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R79" s="23"/>
       <c r="S79" s="30"/>
@@ -10197,7 +10227,7 @@
         <v>23</v>
       </c>
       <c r="V79" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W79" s="30"/>
       <c r="X79" s="31"/>
@@ -10216,34 +10246,34 @@
       </c>
       <c r="AF79" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG79" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH79" s="28" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="80" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A80" s="23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E80" s="25" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G80" s="26">
         <v>46508</v>
@@ -10252,7 +10282,7 @@
         <v>46538</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J80" s="27">
         <f t="shared" si="16"/>
@@ -10270,10 +10300,10 @@
       <c r="N80" s="24"/>
       <c r="O80" s="23"/>
       <c r="P80" s="23" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="Q80" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R80" s="23"/>
       <c r="S80" s="30"/>
@@ -10285,7 +10315,7 @@
         <v>23</v>
       </c>
       <c r="V80" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W80" s="30"/>
       <c r="X80" s="31"/>
@@ -10304,34 +10334,34 @@
       </c>
       <c r="AF80" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG80" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH80" s="28" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="81" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A81" s="23" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B81" s="23" t="s">
         <v>20</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G81" s="26">
         <v>46508</v>
@@ -10340,7 +10370,7 @@
         <v>46538</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J81" s="27">
         <f t="shared" si="16"/>
@@ -10358,10 +10388,10 @@
       <c r="N81" s="24"/>
       <c r="O81" s="23"/>
       <c r="P81" s="23" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Q81" s="23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R81" s="23"/>
       <c r="S81" s="30"/>
@@ -10373,7 +10403,7 @@
         <v>23</v>
       </c>
       <c r="V81" s="30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="W81" s="30"/>
       <c r="X81" s="31"/>
@@ -10392,14 +10422,14 @@
       </c>
       <c r="AF81" s="28">
         <f t="shared" ca="1" si="22"/>
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG81" s="28" t="str">
         <f t="shared" ca="1" si="23"/>
         <v/>
       </c>
       <c r="AH81" s="28" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -10499,11 +10529,12 @@
     <hyperlink ref="S45" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
     <hyperlink ref="S46" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
     <hyperlink ref="S3" r:id="rId33" xr:uid="{F865062C-29FE-4A16-B08E-9C5893CE10A1}"/>
+    <hyperlink ref="S5" r:id="rId34" xr:uid="{EE9EEB41-677F-417E-AEEA-7CBAABEB4947}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId34"/>
+    <tablePart r:id="rId35"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -10604,7 +10635,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D2" s="37" t="s">
         <v>24</v>
@@ -10613,7 +10644,7 @@
         <v>98</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -10624,16 +10655,16 @@
         <v>24</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10644,16 +10675,16 @@
         <v>25</v>
       </c>
       <c r="C4" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="E4" s="37" t="s">
         <v>468</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>470</v>
-      </c>
       <c r="F4" s="37" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -10664,10 +10695,10 @@
         <v>10</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -10705,22 +10736,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="D1" s="36" t="s">
         <v>474</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="E1" s="36" t="s">
         <v>475</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="F1" s="36" t="s">
         <v>476</v>
-      </c>
-      <c r="E1" s="36" t="s">
-        <v>477</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -10731,13 +10762,13 @@
         <v>46291</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D2" s="39" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F11" si="0">B2-A2+1</f>
@@ -10752,13 +10783,13 @@
         <v>46354</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" si="0"/>
@@ -10773,13 +10804,13 @@
         <v>46395</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
@@ -10794,13 +10825,13 @@
         <v>46403</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="0"/>
@@ -10815,13 +10846,13 @@
         <v>46408</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="0"/>
@@ -10836,13 +10867,13 @@
         <v>46422</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="0"/>
@@ -10857,13 +10888,13 @@
         <v>46440</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="0"/>
@@ -10878,13 +10909,13 @@
         <v>46459</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
@@ -10899,13 +10930,13 @@
         <v>46529</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
@@ -10920,13 +10951,13 @@
         <v>46534</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D11" s="39" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="0"/>
@@ -10935,7 +10966,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/events-tracker.xlsx
+++ b/events-tracker.xlsx
@@ -5,11 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261001.7 Interactive Onboarding &amp; SFI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://classerasa-my.sharepoint.com/personal/m_serag_classera_com/Documents/AY26 Classera PS Training Unit Initiatives &amp; Activities/AY26-27 eLearning Plan/Outputs/plans-site V261005/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5E3910-BC54-4FFC-82C5-0A6DD4AD617B}"/>
-  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="GT6RTs28arVuVVbJHNVA+74tm3CsKtOX1/t6N1+DEjtxFsYZb8cyxWH4NbWlgRRSWqb+7Srluyl3yEyEHkL+fg==" workbookSaltValue="z6zQ5x9wttKwXo5UNctm4w==" workbookSpinCount="100000" lockStructure="1"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_B31D5C704978562888068C73A4A5265DB18A4F65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A38B884-53AE-421E-91C6-7791C1EF11EB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2759,11 +2758,11 @@
       </c>
       <c r="D16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,D$15)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,E$15)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F16" s="16">
         <f>COUNTIFS(Events!$U$2:$U$400,F$15)</f>
@@ -3458,7 +3457,7 @@
         <v>Published</v>
       </c>
       <c r="U5" s="30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V5" s="30" t="s">
         <v>466</v>
@@ -6407,7 +6406,7 @@
         <v>25</v>
       </c>
       <c r="V37" s="30" t="s">
-        <v>119</v>
+        <v>469</v>
       </c>
       <c r="W37" s="30"/>
       <c r="X37" s="31"/>
